--- a/mainWidget/mainWidget/src/database/计算模型-殉爆试验.xlsx
+++ b/mainWidget/mainWidget/src/database/计算模型-殉爆试验.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSProject\git\GFApp\mainWidget\mainWidget\src\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B8AA369-EA93-432C-A553-0B610AA75142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{732DD28F-2C32-4511-9EA7-E32D792C49A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1573" uniqueCount="1565">
   <si>
     <t>序号</t>
   </si>
@@ -308,1741 +308,4862 @@
   </si>
   <si>
     <t>10845.3684</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>25028.5502</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>8683.8829</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>40919.2411</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>40199.7149</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>47515.5133</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>35392.0352</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>16303.0529</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>26744.224</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>33322.4841</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>43744.5161</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1172.0833</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>391.4508</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1241.4708</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>27279.2757</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>60536.5929</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1943.9427</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>473.6922</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>843.1182</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>45611.4221</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>20909.6068</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>568.9216</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>464.9967</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>478.9428</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>30173.0208</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>23112.6746</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>498.6154</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>462.1987</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>684.2353</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>50368.2275</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>35928.0445</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>53.7325</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-177.6033</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>937.3439</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>77679.5147</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>49063.1394</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>442.2705</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>167.671</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1434.011</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>84262.2478</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.2905</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.0887</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.3049</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.4258</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.2274</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1449</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0198</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0064</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0078</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1478</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0178</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0068</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0069</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.2198</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0261</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0158</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0381</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.2412</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.3347</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0249</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0279</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1691</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0308</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0191</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0154</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0117</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0661</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1211</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0196</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0079</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0121</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1602</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.5303</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.3872</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.248</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1534</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0395</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.2617</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>4.8487</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>32.4692</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-26.6182</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>13.7478</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.802</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.2299</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.2637</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.3841</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-7.4413</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1748</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1221</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1882</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.4376</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-3.4344</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.4129</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>2.1419</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.9214</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>11.8055</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-8.2976</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.7507</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>2.5195</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.6165</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.9242</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-6.5217</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.7852</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.6003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.4158</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-7.9569</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>3.2763</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.8177</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.5726</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.6978</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-28.7483</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-23.3004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-17.293</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>20.5974</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-6.6908</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0534</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>5.0663</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.6246</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.9453</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.1386</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0562</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.8312</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0168</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0372</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-3.1777</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.5153</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.023</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.068</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0833</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-6.1385</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.3178</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1851</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1557</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.2188</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-6.2982</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.5263</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-3.1044</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1909</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.2343</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.832</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.3533</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-2.1842</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1642</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0335</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0847</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0219</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-2.7671</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.187</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0404</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0581</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0744</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1114</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.2305</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-3.4176</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0321</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.8999</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1349</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.7778</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.3608</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1713</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.3779</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0122</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.047</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0595</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.9708</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.7255</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.2896</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.369</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.3411</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.3312</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.7302</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.8202</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0423</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0085</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0586</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0279</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0317</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1723</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.3393</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.4417</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0807</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.173</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0027</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0602</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.014</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-2.0016</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-3.2322</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0187</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0245</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0645</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.06</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1237</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.092</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>4.1697</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>28.1136</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>46.7979</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-16.9604</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>2.986</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.1874</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.6647</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-49.6803</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-72.6962</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.8771</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.5217</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.6976</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-115.7082</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-129.6052</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>2.1196</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>4.6512</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-7.4925</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-158.2985</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-93.1774</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.5709</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-3.1534</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-11.0371</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-100.456</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>48.6668</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>3.2283</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-2.2587</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-8.795</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-63.1084</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>39.2138</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-93.0068</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-3.542</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.5333</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-68.2541</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-22.4688</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>2.4512</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-14.8728</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-102.8421</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.3818</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.4308</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.2182</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-51.3232</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.5463</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.7455</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.6663</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1892</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0442</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0635</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.8748</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0945</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1133</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-3.6424</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.2336</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1375</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0156</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0145</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-4.1094</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>2.6399</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0889</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0257</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-3.3325</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.4669</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0387</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0758</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0307</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.5524</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.3267</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0839</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0132</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.8007</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.5516</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.3938</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.4175</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.9569</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.785</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-8.4533</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-2.521</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-25.2926</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-2.5107</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.083</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1018</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.2446</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-20.934</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.0328</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0783</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-12.9241</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0801</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.2447</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.592</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-18.7476</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1309</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.9108</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.2008</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.4794</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.3649</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.3407</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.8163</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-49.4956</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.9813</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.442</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.3347</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.767</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.7933</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0233</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-2.4954</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1403</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1841</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.6755</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-10.8288</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-13.4856</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-29.8784</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-36.1278</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-17.8378</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-16.792</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-52.0032</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-13.9199</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-53.0924</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-66.0665</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.3505</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.7787</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-11.5428</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1507</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-21.9795</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-16.63</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.6959</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.0872</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.1948</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.2102</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-41.7689</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-18.7946</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.9566</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.3389</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-61.4556</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>38.0328</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.4674</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.8204</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.2835</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-8.096</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.8695</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-40.5586</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.6995</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-2.723</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-43.7731</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-6.3789</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-2.6769</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.3741</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-2.1299</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-27.1934</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-41.2748</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-27.5984</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-8.4513</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-32.5401</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-64.6019</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-548.5944</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-12.1368</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-2.1217</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-949.3792</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-181.1462</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-12.6588</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-977.603</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-508.0924</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-7.1818</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-511.8165</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-22.341</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-11.8679</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-547.6604</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-871.5728</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.5293</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.9438</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1232.6679</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>36.0152</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>44.3987</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>21.3601</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1171.3884</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1762.9132</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1738.7295</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>24.3704</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>17.4784</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>12.4295</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-2332.0796</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-2030.1137</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>11.3563</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>3.7259</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.3553</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1550.6494</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1216.34</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-17.2241</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>2.3119</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-2.5888</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1073.5453</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-661.8901</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-723.983</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-715.7314</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1213.7246</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-486.7818</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-18.3147</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-16.2081</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-24.1358</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-20.1645</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.6806</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-19.9027</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.8709</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-27.485</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.2207</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.4816</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-8.278</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-10.9695</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-19.6346</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1487</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.2726</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-9.8979</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.6491</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-21.1599</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.349</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.5442</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-17.6213</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-37.0038</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.2906</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.053</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.0176</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-55.8775</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-33.2188</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.7729</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.2651</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.2904</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-32.1351</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-37.0162</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.823</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.2403</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.2861</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-22.7155</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-20.8794</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>9.8565</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-16.8924</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.4485</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-53.3101</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-35.8569</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>-19938.7287+0.1415*B+0.0000*C+12.0132*D-1.0522*E+0.3612*F+0.0000*G-2.0497*H+0.0250*I-18.8483*J-20.5599*K-402.1340*L-18.6415*M</t>
+  </si>
+  <si>
+    <t>-19938.7287</t>
+  </si>
+  <si>
+    <t>0.1415</t>
+  </si>
+  <si>
+    <t>12.0132</t>
+  </si>
+  <si>
+    <t>-1.0522</t>
+  </si>
+  <si>
+    <t>0.3612</t>
+  </si>
+  <si>
+    <t>-2.0497</t>
+  </si>
+  <si>
+    <t>0.025</t>
+  </si>
+  <si>
+    <t>-18.8483</t>
+  </si>
+  <si>
+    <t>-20.5599</t>
+  </si>
+  <si>
+    <t>-402.134</t>
+  </si>
+  <si>
+    <t>-18.6415</t>
+  </si>
+  <si>
+    <t>31359.4343-0.0856*B+0.0000*C+8.2476*D+0.7385*E-0.4811*F+0.0000*G-53.5602*H+1.0475*I-11.4163*J-41.7217*K+510.4677*L+8.6850*M</t>
+  </si>
+  <si>
+    <t>31359.4343</t>
+  </si>
+  <si>
+    <t>-0.0856</t>
+  </si>
+  <si>
+    <t>8.2476</t>
+  </si>
+  <si>
+    <t>0.7385</t>
+  </si>
+  <si>
+    <t>-0.4811</t>
+  </si>
+  <si>
+    <t>-53.5602</t>
+  </si>
+  <si>
+    <t>1.0475</t>
+  </si>
+  <si>
+    <t>-11.4163</t>
+  </si>
+  <si>
+    <t>-41.7217</t>
+  </si>
+  <si>
+    <t>510.4677</t>
+  </si>
+  <si>
+    <t>8.685</t>
+  </si>
+  <si>
+    <t>15228.9215-0.1490*B+0.0000*C+1.1651*D+1.2501*E+0.1670*F+0.0000*G+39.6976*H-0.6674*I-5.6084*J-11.1755*K-1538.3653*L-22.7184*M</t>
+  </si>
+  <si>
+    <t>15228.9215</t>
+  </si>
+  <si>
+    <t>-0.149</t>
+  </si>
+  <si>
+    <t>1.1651</t>
+  </si>
+  <si>
+    <t>1.2501</t>
+  </si>
+  <si>
+    <t>0.167</t>
+  </si>
+  <si>
+    <t>39.6976</t>
+  </si>
+  <si>
+    <t>-0.6674</t>
+  </si>
+  <si>
+    <t>-5.6084</t>
+  </si>
+  <si>
+    <t>-11.1755</t>
+  </si>
+  <si>
+    <t>-1538.3653</t>
+  </si>
+  <si>
+    <t>-22.7184</t>
+  </si>
+  <si>
+    <t>40311.4432+0.2415*B+0.0000*C-6.0085*D+1.7389*E-1.7117*F+0.0000*G-94.2128*H-1.8135*I-12.6665*J-31.4658*K-567.8544*L-20.7585*M</t>
+  </si>
+  <si>
+    <t>40311.4432</t>
+  </si>
+  <si>
+    <t>0.2415</t>
+  </si>
+  <si>
+    <t>-6.0085</t>
+  </si>
+  <si>
+    <t>1.7389</t>
+  </si>
+  <si>
+    <t>-1.7117</t>
+  </si>
+  <si>
+    <t>-94.2128</t>
+  </si>
+  <si>
+    <t>-1.8135</t>
+  </si>
+  <si>
+    <t>-12.6665</t>
+  </si>
+  <si>
+    <t>-31.4658</t>
+  </si>
+  <si>
+    <t>-567.8544</t>
+  </si>
+  <si>
+    <t>-20.7585</t>
+  </si>
+  <si>
+    <t>51658.3099-0.3674*B+0.0000*C-11.9153*D+0.1284*E-1.6519*F+0.0000*G+45.0757*H-1.7573*I-12.7290*J-37.6600*K-1126.6952*L-10.8945*M</t>
+  </si>
+  <si>
+    <t>51658.3099</t>
+  </si>
+  <si>
+    <t>-0.3674</t>
+  </si>
+  <si>
+    <t>-11.9153</t>
+  </si>
+  <si>
+    <t>0.1284</t>
+  </si>
+  <si>
+    <t>-1.6519</t>
+  </si>
+  <si>
+    <t>45.0757</t>
+  </si>
+  <si>
+    <t>-1.7573</t>
+  </si>
+  <si>
+    <t>-12.729</t>
+  </si>
+  <si>
+    <t>-37.66</t>
+  </si>
+  <si>
+    <t>-1126.6952</t>
+  </si>
+  <si>
+    <t>-10.8945</t>
+  </si>
+  <si>
+    <t>33065.0328-0.1539*B+0.0000*C+13.0933*D-0.7177*E-1.0903*F+0.0000*G-70.8298*H-0.2312*I-3.4659*J-15.9338*K-1667.0362*L-26.6522*M</t>
+  </si>
+  <si>
+    <t>33065.0328</t>
+  </si>
+  <si>
+    <t>-0.1539</t>
+  </si>
+  <si>
+    <t>13.0933</t>
+  </si>
+  <si>
+    <t>-0.7177</t>
+  </si>
+  <si>
+    <t>-1.0903</t>
+  </si>
+  <si>
+    <t>-70.8298</t>
+  </si>
+  <si>
+    <t>-0.2312</t>
+  </si>
+  <si>
+    <t>-3.4659</t>
+  </si>
+  <si>
+    <t>-15.9338</t>
+  </si>
+  <si>
+    <t>-1667.0362</t>
+  </si>
+  <si>
+    <t>-26.6522</t>
+  </si>
+  <si>
+    <t>35535.6254+0.2380*B+0.0000*C+10.6006*D-3.3356*E-1.8285*F+0.0000*G-9.3477*H-0.6744*I-14.3693*J+30.1129*K-941.2163*L-2.1267*M</t>
+  </si>
+  <si>
+    <t>35535.6254</t>
+  </si>
+  <si>
+    <t>0.238</t>
+  </si>
+  <si>
+    <t>10.6006</t>
+  </si>
+  <si>
+    <t>-3.3356</t>
+  </si>
+  <si>
+    <t>-1.8285</t>
+  </si>
+  <si>
+    <t>-9.3477</t>
+  </si>
+  <si>
+    <t>-0.6744</t>
+  </si>
+  <si>
+    <t>-14.3693</t>
+  </si>
+  <si>
+    <t>30.1129</t>
+  </si>
+  <si>
+    <t>-941.2163</t>
+  </si>
+  <si>
+    <t>-2.1267</t>
+  </si>
+  <si>
+    <t>-9543.2199+0.1999*B+0.0000*C-13.2730*D+0.7721*E+0.1328*F+0.0000*G-104.5735*H+0.8898*I+2.8967*J-6.4859*K-499.9052*L-11.9957*M</t>
+  </si>
+  <si>
+    <t>-9543.2199</t>
+  </si>
+  <si>
+    <t>0.1999</t>
+  </si>
+  <si>
+    <t>-13.273</t>
+  </si>
+  <si>
+    <t>0.7721</t>
+  </si>
+  <si>
+    <t>0.1328</t>
+  </si>
+  <si>
+    <t>-104.5735</t>
+  </si>
+  <si>
+    <t>0.8898</t>
+  </si>
+  <si>
+    <t>2.8967</t>
+  </si>
+  <si>
+    <t>-6.4859</t>
+  </si>
+  <si>
+    <t>-499.9052</t>
+  </si>
+  <si>
+    <t>-11.9957</t>
+  </si>
+  <si>
+    <t>7552.8072-0.2366*B+0.0000*C-20.0094*D+0.1509*E+1.0558*F+0.0000*G-45.9542*H+2.0621*I-6.2278*J-17.9746*K-570.1005*L-14.9106*M</t>
+  </si>
+  <si>
+    <t>7552.8072</t>
+  </si>
+  <si>
+    <t>-0.2366</t>
+  </si>
+  <si>
+    <t>-20.0094</t>
+  </si>
+  <si>
+    <t>0.1509</t>
+  </si>
+  <si>
+    <t>1.0558</t>
+  </si>
+  <si>
+    <t>-45.9542</t>
+  </si>
+  <si>
+    <t>2.0621</t>
+  </si>
+  <si>
+    <t>-6.2278</t>
+  </si>
+  <si>
+    <t>-17.9746</t>
+  </si>
+  <si>
+    <t>-570.1005</t>
+  </si>
+  <si>
+    <t>-14.9106</t>
+  </si>
+  <si>
+    <t>-37251.2140-0.3605*B+0.0000*C-13.6284*D-6.3184*E-0.3742*F+0.0000*G-39.6471*H-0.8241*I-4.7057*J-15.7364*K-360.4062*L-22.6645*M</t>
+  </si>
+  <si>
+    <t>-37251.214</t>
+  </si>
+  <si>
+    <t>-0.3605</t>
+  </si>
+  <si>
+    <t>-13.6284</t>
+  </si>
+  <si>
+    <t>-6.3184</t>
+  </si>
+  <si>
+    <t>-0.3742</t>
+  </si>
+  <si>
+    <t>-39.6471</t>
+  </si>
+  <si>
+    <t>-0.8241</t>
+  </si>
+  <si>
+    <t>-4.7057</t>
+  </si>
+  <si>
+    <t>-15.7364</t>
+  </si>
+  <si>
+    <t>-360.4062</t>
+  </si>
+  <si>
+    <t>-22.6645</t>
+  </si>
+  <si>
+    <t>-9294.3386+0.0808*B+0.0000*C-5.6475*D-2.8590*E-0.6836*F+0.0000*G-90.0065*H+1.7513*I+1.8919*J-60.8544*K-662.9403*L-33.4359*M</t>
+  </si>
+  <si>
+    <t>-9294.3386</t>
+  </si>
+  <si>
+    <t>0.0808</t>
+  </si>
+  <si>
+    <t>-5.6475</t>
+  </si>
+  <si>
+    <t>-2.859</t>
+  </si>
+  <si>
+    <t>-0.6836</t>
+  </si>
+  <si>
+    <t>-90.0065</t>
+  </si>
+  <si>
+    <t>1.7513</t>
+  </si>
+  <si>
+    <t>1.8919</t>
+  </si>
+  <si>
+    <t>-60.8544</t>
+  </si>
+  <si>
+    <t>-662.9403</t>
+  </si>
+  <si>
+    <t>-33.4359</t>
+  </si>
+  <si>
+    <t>69195.7122-0.2850*B+0.0000*C-13.1906*D-1.0256*E-1.5088*F+0.0000*G+19.3717*H-0.2793*I+4.2583*J+1.0659*K-1574.8320*L-28.6976*M</t>
+  </si>
+  <si>
+    <t>69195.7122</t>
+  </si>
+  <si>
+    <t>-0.285</t>
+  </si>
+  <si>
+    <t>-13.1906</t>
+  </si>
+  <si>
+    <t>-1.0256</t>
+  </si>
+  <si>
+    <t>-1.5088</t>
+  </si>
+  <si>
+    <t>19.3717</t>
+  </si>
+  <si>
+    <t>-0.2793</t>
+  </si>
+  <si>
+    <t>4.2583</t>
+  </si>
+  <si>
+    <t>1.0659</t>
+  </si>
+  <si>
+    <t>-1574.832</t>
+  </si>
+  <si>
+    <t>-28.6976</t>
+  </si>
+  <si>
+    <t>51576.4770+0.2910*B+0.0000*C-14.5356*D-0.8680*E-1.5697*F+0.0000*G-22.0693*H+0.6900*I-1.2097*J-48.4821*K-1001.4633*L-1.7280*M</t>
+  </si>
+  <si>
+    <t>51576.477</t>
+  </si>
+  <si>
+    <t>0.291</t>
+  </si>
+  <si>
+    <t>-14.5356</t>
+  </si>
+  <si>
+    <t>-0.868</t>
+  </si>
+  <si>
+    <t>-1.5697</t>
+  </si>
+  <si>
+    <t>-22.0693</t>
+  </si>
+  <si>
+    <t>0.69</t>
+  </si>
+  <si>
+    <t>-1.2097</t>
+  </si>
+  <si>
+    <t>-48.4821</t>
+  </si>
+  <si>
+    <t>-1001.4633</t>
+  </si>
+  <si>
+    <t>-1.728</t>
+  </si>
+  <si>
+    <t>10856.3028+0.5662*B+0.0000*C-4.7467*D-1.7571*E+0.1920*F+0.0000*G-17.8799*H-0.6955*I+20.7718*J-20.0065*K-260.7603*L-8.6927*M</t>
+  </si>
+  <si>
+    <t>10856.3028</t>
+  </si>
+  <si>
+    <t>0.5662</t>
+  </si>
+  <si>
+    <t>-4.7467</t>
+  </si>
+  <si>
+    <t>-1.7571</t>
+  </si>
+  <si>
+    <t>0.192</t>
+  </si>
+  <si>
+    <t>-17.8799</t>
+  </si>
+  <si>
+    <t>-0.6955</t>
+  </si>
+  <si>
+    <t>20.7718</t>
+  </si>
+  <si>
+    <t>-20.0065</t>
+  </si>
+  <si>
+    <t>-260.7603</t>
+  </si>
+  <si>
+    <t>-8.6927</t>
+  </si>
+  <si>
+    <t>13633.5341-0.2239*B+0.0000*C+18.1801*D-1.9613*E+0.4484*F+0.0000*G-38.6927*H-0.2660*I-12.6519*J+0.9149*K-1649.5798*L+14.1739*M</t>
+  </si>
+  <si>
+    <t>13633.5341</t>
+  </si>
+  <si>
+    <t>-0.2239</t>
+  </si>
+  <si>
+    <t>18.1801</t>
+  </si>
+  <si>
+    <t>-1.9613</t>
+  </si>
+  <si>
+    <t>0.4484</t>
+  </si>
+  <si>
+    <t>-38.6927</t>
+  </si>
+  <si>
+    <t>-0.266</t>
+  </si>
+  <si>
+    <t>-12.6519</t>
+  </si>
+  <si>
+    <t>0.9149</t>
+  </si>
+  <si>
+    <t>-1649.5798</t>
+  </si>
+  <si>
+    <t>14.1739</t>
+  </si>
+  <si>
+    <t>-12840.5845+0.0895*B+0.0000*C+9.7319*D-4.4639*E-0.4618*F+0.0000*G-12.5523*H-2.3857*I-3.6477*J-31.8474*K-657.1862*L+14.8164*M</t>
+  </si>
+  <si>
+    <t>-12840.5845</t>
+  </si>
+  <si>
+    <t>0.0895</t>
+  </si>
+  <si>
+    <t>9.7319</t>
+  </si>
+  <si>
+    <t>-4.4639</t>
+  </si>
+  <si>
+    <t>-0.4618</t>
+  </si>
+  <si>
+    <t>-12.5523</t>
+  </si>
+  <si>
+    <t>-2.3857</t>
+  </si>
+  <si>
+    <t>-3.6477</t>
+  </si>
+  <si>
+    <t>-31.8474</t>
+  </si>
+  <si>
+    <t>-657.1862</t>
+  </si>
+  <si>
+    <t>14.8164</t>
+  </si>
+  <si>
+    <t>33421.6245+0.0535*B+0.0000*C-5.5590*D-3.1929*E-0.7992*F+0.0000*G-38.0297*H+0.2794*I-19.1306*J+11.9386*K-726.8256*L-22.0086*M</t>
+  </si>
+  <si>
+    <t>33421.6245</t>
+  </si>
+  <si>
+    <t>0.0535</t>
+  </si>
+  <si>
+    <t>-5.559</t>
+  </si>
+  <si>
+    <t>-3.1929</t>
+  </si>
+  <si>
+    <t>-0.7992</t>
+  </si>
+  <si>
+    <t>-38.0297</t>
+  </si>
+  <si>
+    <t>0.2794</t>
+  </si>
+  <si>
+    <t>-19.1306</t>
+  </si>
+  <si>
+    <t>11.9386</t>
+  </si>
+  <si>
+    <t>-726.8256</t>
+  </si>
+  <si>
+    <t>-22.0086</t>
+  </si>
+  <si>
+    <t>7258.1725+0.2382*B+0.0000*C+3.9804*D+2.8738*E-0.0020*F+0.0000*G+30.2858*H+2.3729*I-11.6255*J-1.4521*K-689.6900*L+1.5195*M</t>
+  </si>
+  <si>
+    <t>7258.1725</t>
+  </si>
+  <si>
+    <t>0.2382</t>
+  </si>
+  <si>
+    <t>3.9804</t>
+  </si>
+  <si>
+    <t>2.8738</t>
+  </si>
+  <si>
+    <t>-0.002</t>
+  </si>
+  <si>
+    <t>30.2858</t>
+  </si>
+  <si>
+    <t>2.3729</t>
+  </si>
+  <si>
+    <t>-11.6255</t>
+  </si>
+  <si>
+    <t>-1.4521</t>
+  </si>
+  <si>
+    <t>-689.69</t>
+  </si>
+  <si>
+    <t>1.5195</t>
+  </si>
+  <si>
+    <t>7056.0741+0.4440*B+0.0000*C+5.8683*D-2.3191*E+0.0592*F+0.0000*G-48.9183*H-0.1261*I+9.1245*J+15.3719*K-1733.8510*L-8.4413*M</t>
+  </si>
+  <si>
+    <t>7056.0741</t>
+  </si>
+  <si>
+    <t>0.444</t>
+  </si>
+  <si>
+    <t>5.8683</t>
+  </si>
+  <si>
+    <t>-2.3191</t>
+  </si>
+  <si>
+    <t>0.0592</t>
+  </si>
+  <si>
+    <t>-48.9183</t>
+  </si>
+  <si>
+    <t>-0.1261</t>
+  </si>
+  <si>
+    <t>9.1245</t>
+  </si>
+  <si>
+    <t>15.3719</t>
+  </si>
+  <si>
+    <t>-1733.851</t>
+  </si>
+  <si>
+    <t>-8.4413</t>
+  </si>
+  <si>
+    <t>13181.4761+0.1868*B+0.0000*C-5.0940*D+0.3598*E-1.5093*F+0.0000*G-7.2974*H-1.3023*I-1.2829*J-19.8769*K+257.6255*L+10.3513*M</t>
+  </si>
+  <si>
+    <t>13181.4761</t>
+  </si>
+  <si>
+    <t>0.1868</t>
+  </si>
+  <si>
+    <t>-5.094</t>
+  </si>
+  <si>
+    <t>0.3598</t>
+  </si>
+  <si>
+    <t>-1.5093</t>
+  </si>
+  <si>
+    <t>-7.2974</t>
+  </si>
+  <si>
+    <t>-1.3023</t>
+  </si>
+  <si>
+    <t>-1.2829</t>
+  </si>
+  <si>
+    <t>-19.8769</t>
+  </si>
+  <si>
+    <t>257.6255</t>
+  </si>
+  <si>
+    <t>10.3513</t>
+  </si>
+  <si>
+    <t>5601.4910+0.7931*B+0.0000*C+3.4828*D+0.0698*E-0.6416*F+0.0000*G-97.5757*H-1.0451*I-7.5569*J+5.4692*K-1230.6893*L-27.3402*M</t>
+  </si>
+  <si>
+    <t>5601.491</t>
+  </si>
+  <si>
+    <t>0.7931</t>
+  </si>
+  <si>
+    <t>3.4828</t>
+  </si>
+  <si>
+    <t>0.0698</t>
+  </si>
+  <si>
+    <t>-0.6416</t>
+  </si>
+  <si>
+    <t>-97.5757</t>
+  </si>
+  <si>
+    <t>-1.0451</t>
+  </si>
+  <si>
+    <t>-7.5569</t>
+  </si>
+  <si>
+    <t>5.4692</t>
+  </si>
+  <si>
+    <t>-1230.6893</t>
+  </si>
+  <si>
+    <t>-27.3402</t>
+  </si>
+  <si>
+    <t>15476.1559-0.0884*B+0.0000*C-11.9097*D-0.3928*E-0.8677*F+0.0000*G+28.0701*H+0.9177*I-32.9514*J-24.1750*K-682.4933*L+4.2433*M</t>
+  </si>
+  <si>
+    <t>15476.1559</t>
+  </si>
+  <si>
+    <t>-0.0884</t>
+  </si>
+  <si>
+    <t>-11.9097</t>
+  </si>
+  <si>
+    <t>-0.3928</t>
+  </si>
+  <si>
+    <t>-0.8677</t>
+  </si>
+  <si>
+    <t>28.0701</t>
+  </si>
+  <si>
+    <t>0.9177</t>
+  </si>
+  <si>
+    <t>-32.9514</t>
+  </si>
+  <si>
+    <t>-24.175</t>
+  </si>
+  <si>
+    <t>-682.4933</t>
+  </si>
+  <si>
+    <t>4.2433</t>
+  </si>
+  <si>
+    <t>6425.1951-0.0099*B+0.0000*C+11.9507*D+1.6815*E+0.1447*F+0.0000*G-90.6411*H+1.6705*I-8.3799*J-24.8124*K-264.7414*L+7.5072*M</t>
+  </si>
+  <si>
+    <t>6425.1951</t>
+  </si>
+  <si>
+    <t>-0.0099</t>
+  </si>
+  <si>
+    <t>11.9507</t>
+  </si>
+  <si>
+    <t>1.6815</t>
+  </si>
+  <si>
+    <t>0.1447</t>
+  </si>
+  <si>
+    <t>-90.6411</t>
+  </si>
+  <si>
+    <t>1.6705</t>
+  </si>
+  <si>
+    <t>-8.3799</t>
+  </si>
+  <si>
+    <t>-24.8124</t>
+  </si>
+  <si>
+    <t>-264.7414</t>
+  </si>
+  <si>
+    <t>7.5072</t>
+  </si>
+  <si>
+    <t>26812.7291+0.0483*B+0.0000*C+8.4121*D+3.8868*E-1.1290*F+0.0000*G-21.8753*H+2.9569*I-1.5164*J-59.1856*K+281.9596*L-18.4715*M</t>
+  </si>
+  <si>
+    <t>26812.7291</t>
+  </si>
+  <si>
+    <t>0.0483</t>
+  </si>
+  <si>
+    <t>8.4121</t>
+  </si>
+  <si>
+    <t>3.8868</t>
+  </si>
+  <si>
+    <t>-1.129</t>
+  </si>
+  <si>
+    <t>-21.8753</t>
+  </si>
+  <si>
+    <t>2.9569</t>
+  </si>
+  <si>
+    <t>-1.5164</t>
+  </si>
+  <si>
+    <t>-59.1856</t>
+  </si>
+  <si>
+    <t>281.9596</t>
+  </si>
+  <si>
+    <t>-18.4715</t>
+  </si>
+  <si>
+    <t>-8682.1739+0.2133*B+0.0000*C-4.2443*D-1.3422*E-0.8164*F+0.0000*G+13.1697*H-0.2229*I+11.5849*J-7.8215*K-894.3262*L+1.8620*M</t>
+  </si>
+  <si>
+    <t>-8682.1739</t>
+  </si>
+  <si>
+    <t>0.2133</t>
+  </si>
+  <si>
+    <t>-4.2443</t>
+  </si>
+  <si>
+    <t>-1.3422</t>
+  </si>
+  <si>
+    <t>-0.8164</t>
+  </si>
+  <si>
+    <t>13.1697</t>
+  </si>
+  <si>
+    <t>-0.2229</t>
+  </si>
+  <si>
+    <t>11.5849</t>
+  </si>
+  <si>
+    <t>-7.8215</t>
+  </si>
+  <si>
+    <t>-894.3262</t>
+  </si>
+  <si>
+    <t>1.862</t>
+  </si>
+  <si>
+    <t>46942.1981-0.4655*B+0.0000*C+7.6020*D-1.1155*E-0.0274*F+0.0000*G-4.3268*H+3.1713*I+17.4837*J+0.7859*K-967.3062*L-23.4983*M</t>
+  </si>
+  <si>
+    <t>46942.1981</t>
+  </si>
+  <si>
+    <t>-0.4655</t>
+  </si>
+  <si>
+    <t>7.602</t>
+  </si>
+  <si>
+    <t>-1.1155</t>
+  </si>
+  <si>
+    <t>-0.0274</t>
+  </si>
+  <si>
+    <t>-4.3268</t>
+  </si>
+  <si>
+    <t>3.1713</t>
+  </si>
+  <si>
+    <t>17.4837</t>
+  </si>
+  <si>
+    <t>0.7859</t>
+  </si>
+  <si>
+    <t>-967.3062</t>
+  </si>
+  <si>
+    <t>-23.4983</t>
+  </si>
+  <si>
+    <t>16989.3691+0.1818*B+0.0000*C-3.8897*D-2.2205*E+0.8097*F+0.0000*G-81.2201*H+0.7039*I-20.3702*J-12.2242*K-1158.6759*L-10.7750*M</t>
+  </si>
+  <si>
+    <t>16989.3691</t>
+  </si>
+  <si>
+    <t>0.1818</t>
+  </si>
+  <si>
+    <t>-3.8897</t>
+  </si>
+  <si>
+    <t>-2.2205</t>
+  </si>
+  <si>
+    <t>0.8097</t>
+  </si>
+  <si>
+    <t>-81.2201</t>
+  </si>
+  <si>
+    <t>0.7039</t>
+  </si>
+  <si>
+    <t>-20.3702</t>
+  </si>
+  <si>
+    <t>-12.2242</t>
+  </si>
+  <si>
+    <t>-1158.6759</t>
+  </si>
+  <si>
+    <t>-10.775</t>
+  </si>
+  <si>
+    <t>-1353.4659-0.4037*B+0.0000*C+1.1408*D-1.6252*E-0.4409*F+0.0000*G+120.4218*H+3.5394*I+12.5944*J+6.8348*K+661.3714*L-16.9759*M</t>
+  </si>
+  <si>
+    <t>-1353.4659</t>
+  </si>
+  <si>
+    <t>-0.4037</t>
+  </si>
+  <si>
+    <t>1.1408</t>
+  </si>
+  <si>
+    <t>-1.6252</t>
+  </si>
+  <si>
+    <t>-0.4409</t>
+  </si>
+  <si>
+    <t>120.4218</t>
+  </si>
+  <si>
+    <t>3.5394</t>
+  </si>
+  <si>
+    <t>12.5944</t>
+  </si>
+  <si>
+    <t>6.8348</t>
+  </si>
+  <si>
+    <t>661.3714</t>
+  </si>
+  <si>
+    <t>-16.9759</t>
+  </si>
+  <si>
+    <t>32852.3416-0.2068*B+0.0000*C+5.5604*D-0.3961*E-0.1023*F+0.0000*G+38.3759*H+1.8596*I-9.9446*J-13.4275*K+462.7946*L-13.8566*M</t>
+  </si>
+  <si>
+    <t>32852.3416</t>
+  </si>
+  <si>
+    <t>-0.2068</t>
+  </si>
+  <si>
+    <t>5.5604</t>
+  </si>
+  <si>
+    <t>-0.3961</t>
+  </si>
+  <si>
+    <t>-0.1023</t>
+  </si>
+  <si>
+    <t>38.3759</t>
+  </si>
+  <si>
+    <t>1.8596</t>
+  </si>
+  <si>
+    <t>-9.9446</t>
+  </si>
+  <si>
+    <t>-13.4275</t>
+  </si>
+  <si>
+    <t>462.7946</t>
+  </si>
+  <si>
+    <t>-13.8566</t>
+  </si>
+  <si>
+    <t>44700.5381+0.2752*B+0.0000*C+0.0913*D-3.1273*E-0.2151*F+0.0000*G+31.5734*H-0.8427*I-19.6320*J-10.5809*K-338.1095*L-14.1872*M</t>
+  </si>
+  <si>
+    <t>44700.5381</t>
+  </si>
+  <si>
+    <t>0.2752</t>
+  </si>
+  <si>
+    <t>0.0913</t>
+  </si>
+  <si>
+    <t>-3.1273</t>
+  </si>
+  <si>
+    <t>-0.2151</t>
+  </si>
+  <si>
+    <t>31.5734</t>
+  </si>
+  <si>
+    <t>-0.8427</t>
+  </si>
+  <si>
+    <t>-19.632</t>
+  </si>
+  <si>
+    <t>-10.5809</t>
+  </si>
+  <si>
+    <t>-338.1095</t>
+  </si>
+  <si>
+    <t>-14.1872</t>
+  </si>
+  <si>
+    <t>8801.3918-0.0859*B+0.0000*C-11.3098*D+0.2075*E-1.4520*F+0.0000*G-111.7123*H-0.0542*I+18.8174*J+45.7589*K-1892.7376*L-5.0053*M</t>
+  </si>
+  <si>
+    <t>8801.3918</t>
+  </si>
+  <si>
+    <t>-0.0859</t>
+  </si>
+  <si>
+    <t>-11.3098</t>
+  </si>
+  <si>
+    <t>0.2075</t>
+  </si>
+  <si>
+    <t>-1.452</t>
+  </si>
+  <si>
+    <t>-111.7123</t>
+  </si>
+  <si>
+    <t>-0.0542</t>
+  </si>
+  <si>
+    <t>18.8174</t>
+  </si>
+  <si>
+    <t>45.7589</t>
+  </si>
+  <si>
+    <t>-1892.7376</t>
+  </si>
+  <si>
+    <t>-5.0053</t>
+  </si>
+  <si>
+    <t>33895.3057+0.2938*B+0.0000*C+13.1410*D-0.9896*E-0.5958*F+0.0000*G-26.8901*H+0.3527*I-29.2796*J-29.1034*K-1351.0375*L-12.6716*M</t>
+  </si>
+  <si>
+    <t>33895.3057</t>
+  </si>
+  <si>
+    <t>0.2938</t>
+  </si>
+  <si>
+    <t>13.141</t>
+  </si>
+  <si>
+    <t>-0.9896</t>
+  </si>
+  <si>
+    <t>-0.5958</t>
+  </si>
+  <si>
+    <t>-26.8901</t>
+  </si>
+  <si>
+    <t>0.3527</t>
+  </si>
+  <si>
+    <t>-29.2796</t>
+  </si>
+  <si>
+    <t>-29.1034</t>
+  </si>
+  <si>
+    <t>-1351.0375</t>
+  </si>
+  <si>
+    <t>-12.6716</t>
+  </si>
+  <si>
+    <t>28915.5478-0.0323*B+0.0000*C+8.7363*D-1.0409*E+0.7563*F+0.0000*G-47.0622*H+0.1565*I-13.9584*J-16.6782*K+91.6016*L-14.1533*M</t>
+  </si>
+  <si>
+    <t>28915.5478</t>
+  </si>
+  <si>
+    <t>-0.0323</t>
+  </si>
+  <si>
+    <t>8.7363</t>
+  </si>
+  <si>
+    <t>-1.0409</t>
+  </si>
+  <si>
+    <t>0.7563</t>
+  </si>
+  <si>
+    <t>-47.0622</t>
+  </si>
+  <si>
+    <t>0.1565</t>
+  </si>
+  <si>
+    <t>-13.9584</t>
+  </si>
+  <si>
+    <t>-16.6782</t>
+  </si>
+  <si>
+    <t>91.6016</t>
+  </si>
+  <si>
+    <t>-14.1533</t>
+  </si>
+  <si>
+    <t>17131.7984+0.2513*B+0.0000*C+11.3275*D-1.3476*E+0.0161*F+0.0000*G-132.3920*H+0.0779*I-21.2125*J+4.9256*K-1865.0037*L-12.0513*M</t>
+  </si>
+  <si>
+    <t>17131.7984</t>
+  </si>
+  <si>
+    <t>0.2513</t>
+  </si>
+  <si>
+    <t>11.3275</t>
+  </si>
+  <si>
+    <t>-1.3476</t>
+  </si>
+  <si>
+    <t>0.0161</t>
+  </si>
+  <si>
+    <t>-132.392</t>
+  </si>
+  <si>
+    <t>0.0779</t>
+  </si>
+  <si>
+    <t>-21.2125</t>
+  </si>
+  <si>
+    <t>4.9256</t>
+  </si>
+  <si>
+    <t>-1865.0037</t>
+  </si>
+  <si>
+    <t>-12.0513</t>
+  </si>
+  <si>
+    <t>-7352.6866+0.1036*B+0.0000*C-7.3113*D+4.7495*E-0.3031*F+0.0000*G-79.8681*H+0.5079*I-18.7474*J-50.7920*K-352.4345*L-39.4899*M</t>
+  </si>
+  <si>
+    <t>-7352.6866</t>
+  </si>
+  <si>
+    <t>0.1036</t>
+  </si>
+  <si>
+    <t>-7.3113</t>
+  </si>
+  <si>
+    <t>4.7495</t>
+  </si>
+  <si>
+    <t>-0.3031</t>
+  </si>
+  <si>
+    <t>-79.8681</t>
+  </si>
+  <si>
+    <t>0.5079</t>
+  </si>
+  <si>
+    <t>-18.7474</t>
+  </si>
+  <si>
+    <t>-50.792</t>
+  </si>
+  <si>
+    <t>-352.4345</t>
+  </si>
+  <si>
+    <t>-39.4899</t>
+  </si>
+  <si>
+    <t>25066.6542+0.0137*B+0.0000*C+12.2955*D-1.4218*E+0.1732*F+0.0000*G-35.0139*H-0.3636*I-10.2122*J-19.3554*K-510.6743*L-9.7896*M</t>
+  </si>
+  <si>
+    <t>25066.6542</t>
+  </si>
+  <si>
+    <t>0.0137</t>
+  </si>
+  <si>
+    <t>12.2955</t>
+  </si>
+  <si>
+    <t>-1.4218</t>
+  </si>
+  <si>
+    <t>0.1732</t>
+  </si>
+  <si>
+    <t>-35.0139</t>
+  </si>
+  <si>
+    <t>-0.3636</t>
+  </si>
+  <si>
+    <t>-10.2122</t>
+  </si>
+  <si>
+    <t>-19.3554</t>
+  </si>
+  <si>
+    <t>-510.6743</t>
+  </si>
+  <si>
+    <t>-9.7896</t>
+  </si>
+  <si>
+    <t>-26956.5092+0.2497*B+0.0000*C-3.5112*D-2.8560*E-0.5535*F+0.0000*G-69.4934*H-0.2249*I-8.2680*J-40.6132*K-421.6459*L-24.2395*M</t>
+  </si>
+  <si>
+    <t>-26956.5092</t>
+  </si>
+  <si>
+    <t>0.2497</t>
+  </si>
+  <si>
+    <t>-3.5112</t>
+  </si>
+  <si>
+    <t>-2.856</t>
+  </si>
+  <si>
+    <t>-0.5535</t>
+  </si>
+  <si>
+    <t>-69.4934</t>
+  </si>
+  <si>
+    <t>-0.2249</t>
+  </si>
+  <si>
+    <t>-8.268</t>
+  </si>
+  <si>
+    <t>-40.6132</t>
+  </si>
+  <si>
+    <t>-421.6459</t>
+  </si>
+  <si>
+    <t>-24.2395</t>
+  </si>
+  <si>
+    <t>30966.2159-0.5077*B+0.0000*C+0.9147*D-1.6839*E-0.7098*F+0.0000*G+45.9221*H-0.7073*I-2.0712*J+7.2537*K+445.9433*L-26.2732*M</t>
+  </si>
+  <si>
+    <t>30966.2159</t>
+  </si>
+  <si>
+    <t>-0.5077</t>
+  </si>
+  <si>
+    <t>0.9147</t>
+  </si>
+  <si>
+    <t>-1.6839</t>
+  </si>
+  <si>
+    <t>-0.7098</t>
+  </si>
+  <si>
+    <t>45.9221</t>
+  </si>
+  <si>
+    <t>-0.7073</t>
+  </si>
+  <si>
+    <t>-2.0712</t>
+  </si>
+  <si>
+    <t>7.2537</t>
+  </si>
+  <si>
+    <t>445.9433</t>
+  </si>
+  <si>
+    <t>-26.2732</t>
+  </si>
+  <si>
+    <t>47635.7147-0.1698*B+0.0000*C-14.2614*D+2.0974*E-0.9457*F+0.0000*G-15.3529*H+1.0509*I+12.7540*J-17.4917*K-738.6860*L-17.8038*M</t>
+  </si>
+  <si>
+    <t>47635.7147</t>
+  </si>
+  <si>
+    <t>-0.1698</t>
+  </si>
+  <si>
+    <t>-14.2614</t>
+  </si>
+  <si>
+    <t>2.0974</t>
+  </si>
+  <si>
+    <t>-0.9457</t>
+  </si>
+  <si>
+    <t>-15.3529</t>
+  </si>
+  <si>
+    <t>1.0509</t>
+  </si>
+  <si>
+    <t>12.754</t>
+  </si>
+  <si>
+    <t>-17.4917</t>
+  </si>
+  <si>
+    <t>-738.686</t>
+  </si>
+  <si>
+    <t>-17.8038</t>
+  </si>
+  <si>
+    <t>20354.9628+0.3108*B+0.0000*C-23.1889*D-1.1017*E+0.1940*F+0.0000*G+9.2787*H-2.4341*I+5.8554*J-14.8820*K-1197.8066*L-26.9013*M</t>
+  </si>
+  <si>
+    <t>20354.9628</t>
+  </si>
+  <si>
+    <t>0.3108</t>
+  </si>
+  <si>
+    <t>-23.1889</t>
+  </si>
+  <si>
+    <t>-1.1017</t>
+  </si>
+  <si>
+    <t>0.194</t>
+  </si>
+  <si>
+    <t>9.2787</t>
+  </si>
+  <si>
+    <t>-2.4341</t>
+  </si>
+  <si>
+    <t>5.8554</t>
+  </si>
+  <si>
+    <t>-14.882</t>
+  </si>
+  <si>
+    <t>-1197.8066</t>
+  </si>
+  <si>
+    <t>-26.9013</t>
+  </si>
+  <si>
+    <t>6364.3407-0.0166*B+0.0000*C+10.7430*D-2.3654*E-1.3913*F+0.0000*G-73.9102*H-0.6580*I-30.7769*J+12.6996*K-552.0890*L-3.4561*M</t>
+  </si>
+  <si>
+    <t>6364.3407</t>
+  </si>
+  <si>
+    <t>-0.0166</t>
+  </si>
+  <si>
+    <t>10.743</t>
+  </si>
+  <si>
+    <t>-2.3654</t>
+  </si>
+  <si>
+    <t>-1.3913</t>
+  </si>
+  <si>
+    <t>-73.9102</t>
+  </si>
+  <si>
+    <t>-0.658</t>
+  </si>
+  <si>
+    <t>-30.7769</t>
+  </si>
+  <si>
+    <t>12.6996</t>
+  </si>
+  <si>
+    <t>-552.089</t>
+  </si>
+  <si>
+    <t>-3.4561</t>
+  </si>
+  <si>
+    <t>34251.5571+0.0910*B+0.0000*C-4.6800*D-3.1516*E-0.7193*F+0.0000*G-32.6947*H+0.4066*I+4.9823*J+11.1733*K-1225.9181*L-13.4093*M</t>
+  </si>
+  <si>
+    <t>34251.5571</t>
+  </si>
+  <si>
+    <t>0.091</t>
+  </si>
+  <si>
+    <t>-4.68</t>
+  </si>
+  <si>
+    <t>-3.1516</t>
+  </si>
+  <si>
+    <t>-0.7193</t>
+  </si>
+  <si>
+    <t>-32.6947</t>
+  </si>
+  <si>
+    <t>0.4066</t>
+  </si>
+  <si>
+    <t>4.9823</t>
+  </si>
+  <si>
+    <t>11.1733</t>
+  </si>
+  <si>
+    <t>-1225.9181</t>
+  </si>
+  <si>
+    <t>-13.4093</t>
+  </si>
+  <si>
+    <t>29425.8438+0.0695*B+0.0000*C+13.5026*D-1.0808*E+0.6273*F+0.0000*G-40.5686*H-0.8484*I-23.0319*J+2.1094*K+333.6904*L-1.1003*M</t>
+  </si>
+  <si>
+    <t>29425.8438</t>
+  </si>
+  <si>
+    <t>0.0695</t>
+  </si>
+  <si>
+    <t>13.5026</t>
+  </si>
+  <si>
+    <t>-1.0808</t>
+  </si>
+  <si>
+    <t>0.6273</t>
+  </si>
+  <si>
+    <t>-40.5686</t>
+  </si>
+  <si>
+    <t>-0.8484</t>
+  </si>
+  <si>
+    <t>-23.0319</t>
+  </si>
+  <si>
+    <t>2.1094</t>
+  </si>
+  <si>
+    <t>333.6904</t>
+  </si>
+  <si>
+    <t>-1.1003</t>
+  </si>
+  <si>
+    <t>15069.0244+0.2433*B+0.0000*C-8.7920*D+1.7809*E-1.8293*F+0.0000*G-45.5277*H-2.2125*I-11.5755*J-42.1597*K-663.6598*L-3.7130*M</t>
+  </si>
+  <si>
+    <t>15069.0244</t>
+  </si>
+  <si>
+    <t>0.2433</t>
+  </si>
+  <si>
+    <t>-8.792</t>
+  </si>
+  <si>
+    <t>1.7809</t>
+  </si>
+  <si>
+    <t>-1.8293</t>
+  </si>
+  <si>
+    <t>-45.5277</t>
+  </si>
+  <si>
+    <t>-2.2125</t>
+  </si>
+  <si>
+    <t>-11.5755</t>
+  </si>
+  <si>
+    <t>-42.1597</t>
+  </si>
+  <si>
+    <t>-663.6598</t>
+  </si>
+  <si>
+    <t>-3.713</t>
+  </si>
+  <si>
+    <t>20824.2708+0.1497*B+0.0000*C-3.5515*D+1.3315*E+0.4485*F+0.0000*G-95.5541*H+1.0228*I+4.0003*J+7.3979*K-370.3221*L-30.1220*M</t>
+  </si>
+  <si>
+    <t>20824.2708</t>
+  </si>
+  <si>
+    <t>0.1497</t>
+  </si>
+  <si>
+    <t>-3.5515</t>
+  </si>
+  <si>
+    <t>1.3315</t>
+  </si>
+  <si>
+    <t>0.4485</t>
+  </si>
+  <si>
+    <t>-95.5541</t>
+  </si>
+  <si>
+    <t>1.0228</t>
+  </si>
+  <si>
+    <t>4.0003</t>
+  </si>
+  <si>
+    <t>7.3979</t>
+  </si>
+  <si>
+    <t>-370.3221</t>
+  </si>
+  <si>
+    <t>-30.122</t>
+  </si>
+  <si>
+    <t>41048.8860-0.0084*B+0.0000*C+2.4808*D-4.9608*E+0.1877*F+0.0000*G+15.7773*H+2.4722*I+8.8935*J-19.4899*K+541.8627*L-31.2426*M</t>
+  </si>
+  <si>
+    <t>41048.886</t>
+  </si>
+  <si>
+    <t>-0.0084</t>
+  </si>
+  <si>
+    <t>2.4808</t>
+  </si>
+  <si>
+    <t>-4.9608</t>
+  </si>
+  <si>
+    <t>0.1877</t>
+  </si>
+  <si>
+    <t>15.7773</t>
+  </si>
+  <si>
+    <t>2.4722</t>
+  </si>
+  <si>
+    <t>8.8935</t>
+  </si>
+  <si>
+    <t>-19.4899</t>
+  </si>
+  <si>
+    <t>541.8627</t>
+  </si>
+  <si>
+    <t>-31.2426</t>
+  </si>
+  <si>
+    <t>91577.1366+0.7931*B+0.0000*C+8.4041*D-2.2634*E-0.2916*F+0.0000*G+7.7213*H+0.2000*I+2.1195*J+8.1082*K-904.0557*L-10.5652*M</t>
+  </si>
+  <si>
+    <t>91577.1366</t>
+  </si>
+  <si>
+    <t>8.4041</t>
+  </si>
+  <si>
+    <t>-2.2634</t>
+  </si>
+  <si>
+    <t>-0.2916</t>
+  </si>
+  <si>
+    <t>7.7213</t>
+  </si>
+  <si>
+    <t>0.2</t>
+  </si>
+  <si>
+    <t>2.1195</t>
+  </si>
+  <si>
+    <t>8.1082</t>
+  </si>
+  <si>
+    <t>-904.0557</t>
+  </si>
+  <si>
+    <t>-10.5652</t>
+  </si>
+  <si>
+    <t>19196.2793+0.1100*B+0.0000*C+6.8571*D-4.2568*E-0.3097*F+0.0000*G+59.0907*H-0.7551*I-17.2316*J-31.5886*K-94.6747*L-36.8440*M</t>
+  </si>
+  <si>
+    <t>19196.2793</t>
+  </si>
+  <si>
+    <t>0.11</t>
+  </si>
+  <si>
+    <t>6.8571</t>
+  </si>
+  <si>
+    <t>-4.2568</t>
+  </si>
+  <si>
+    <t>-0.3097</t>
+  </si>
+  <si>
+    <t>59.0907</t>
+  </si>
+  <si>
+    <t>-0.7551</t>
+  </si>
+  <si>
+    <t>-17.2316</t>
+  </si>
+  <si>
+    <t>-31.5886</t>
+  </si>
+  <si>
+    <t>-94.6747</t>
+  </si>
+  <si>
+    <t>-36.844</t>
+  </si>
+  <si>
+    <t>26408.8096-0.6781*B+0.0000*C+16.1635*D-0.6983*E+0.6594*F+0.0000*G-54.9109*H+0.0935*I+21.9745*J-39.2774*K+57.8570*L-42.7409*M</t>
+  </si>
+  <si>
+    <t>26408.8096</t>
+  </si>
+  <si>
+    <t>-0.6781</t>
+  </si>
+  <si>
+    <t>16.1635</t>
+  </si>
+  <si>
+    <t>-0.6983</t>
+  </si>
+  <si>
+    <t>0.6594</t>
+  </si>
+  <si>
+    <t>-54.9109</t>
+  </si>
+  <si>
+    <t>0.0935</t>
+  </si>
+  <si>
+    <t>21.9745</t>
+  </si>
+  <si>
+    <t>-39.2774</t>
+  </si>
+  <si>
+    <t>57.857</t>
+  </si>
+  <si>
+    <t>-42.7409</t>
+  </si>
+  <si>
+    <t>-39566.5398+0.2264*B+0.0000*C-0.4393*D-1.5269*E-0.4077*F+0.0000*G-52.8892*H+0.1274*I+2.8334*J+6.2723*K-560.9726*L-1.1790*M</t>
+  </si>
+  <si>
+    <t>-39566.5398</t>
+  </si>
+  <si>
+    <t>0.2264</t>
+  </si>
+  <si>
+    <t>-0.4393</t>
+  </si>
+  <si>
+    <t>-1.5269</t>
+  </si>
+  <si>
+    <t>-0.4077</t>
+  </si>
+  <si>
+    <t>-52.8892</t>
+  </si>
+  <si>
+    <t>0.1274</t>
+  </si>
+  <si>
+    <t>2.8334</t>
+  </si>
+  <si>
+    <t>6.2723</t>
+  </si>
+  <si>
+    <t>-560.9726</t>
+  </si>
+  <si>
+    <t>-1.179</t>
+  </si>
+  <si>
+    <t>37289.9344+0.1539*B+0.0000*C-6.6236*D-5.8901*E-0.5491*F+0.0000*G-38.9170*H-2.2801*I+3.0402*J-15.9493*K-1475.0007*L-0.5469*M</t>
+  </si>
+  <si>
+    <t>37289.9344</t>
+  </si>
+  <si>
+    <t>0.1539</t>
+  </si>
+  <si>
+    <t>-6.6236</t>
+  </si>
+  <si>
+    <t>-5.8901</t>
+  </si>
+  <si>
+    <t>-0.5491</t>
+  </si>
+  <si>
+    <t>-38.917</t>
+  </si>
+  <si>
+    <t>-2.2801</t>
+  </si>
+  <si>
+    <t>3.0402</t>
+  </si>
+  <si>
+    <t>-15.9493</t>
+  </si>
+  <si>
+    <t>-1475.0007</t>
+  </si>
+  <si>
+    <t>-0.5469</t>
+  </si>
+  <si>
+    <t>39720.7548+0.3461*B+0.0000*C-13.9552*D+0.4782*E-1.0540*F+0.0000*G-169.0310*H-0.9232*I-10.0397*J+33.4773*K-352.8226*L+7.4058*M</t>
+  </si>
+  <si>
+    <t>39720.7548</t>
+  </si>
+  <si>
+    <t>0.3461</t>
+  </si>
+  <si>
+    <t>-13.9552</t>
+  </si>
+  <si>
+    <t>0.4782</t>
+  </si>
+  <si>
+    <t>-1.054</t>
+  </si>
+  <si>
+    <t>-169.031</t>
+  </si>
+  <si>
+    <t>-0.9232</t>
+  </si>
+  <si>
+    <t>-10.0397</t>
+  </si>
+  <si>
+    <t>33.4773</t>
+  </si>
+  <si>
+    <t>-352.8226</t>
+  </si>
+  <si>
+    <t>7.4058</t>
+  </si>
+  <si>
+    <t>10875.8760+0.2810*B+0.0000*C-13.5228*D+1.5940*E-1.3517*F+0.0000*G+39.3880*H-0.3672*I-14.4367*J-39.3557*K+10.1583*L-24.9476*M</t>
+  </si>
+  <si>
+    <t>10875.876</t>
+  </si>
+  <si>
+    <t>0.281</t>
+  </si>
+  <si>
+    <t>-13.5228</t>
+  </si>
+  <si>
+    <t>1.594</t>
+  </si>
+  <si>
+    <t>-1.3517</t>
+  </si>
+  <si>
+    <t>39.388</t>
+  </si>
+  <si>
+    <t>-0.3672</t>
+  </si>
+  <si>
+    <t>-14.4367</t>
+  </si>
+  <si>
+    <t>-39.3557</t>
+  </si>
+  <si>
+    <t>10.1583</t>
+  </si>
+  <si>
+    <t>-24.9476</t>
+  </si>
+  <si>
+    <t>27895.6423-0.0731*B+0.0000*C+0.9537*D-0.5313*E-0.8899*F+0.0000*G-76.8513*H-1.9142*I-1.0080*J-12.8584*K+655.8749*L-10.4736*M</t>
+  </si>
+  <si>
+    <t>27895.6423</t>
+  </si>
+  <si>
+    <t>-0.0731</t>
+  </si>
+  <si>
+    <t>0.9537</t>
+  </si>
+  <si>
+    <t>-0.5313</t>
+  </si>
+  <si>
+    <t>-0.8899</t>
+  </si>
+  <si>
+    <t>-76.8513</t>
+  </si>
+  <si>
+    <t>-1.9142</t>
+  </si>
+  <si>
+    <t>-1.008</t>
+  </si>
+  <si>
+    <t>-12.8584</t>
+  </si>
+  <si>
+    <t>655.8749</t>
+  </si>
+  <si>
+    <t>-10.4736</t>
+  </si>
+  <si>
+    <t>-20300.9590+0.4125*B+0.0000*C-13.6903*D+0.8811*E-0.7640*F+0.0000*G+11.3890*H-0.4850*I-18.0643*J-37.5888*K-1204.5339*L-22.3244*M</t>
+  </si>
+  <si>
+    <t>-20300.959</t>
+  </si>
+  <si>
+    <t>0.4125</t>
+  </si>
+  <si>
+    <t>-13.6903</t>
+  </si>
+  <si>
+    <t>0.8811</t>
+  </si>
+  <si>
+    <t>-0.764</t>
+  </si>
+  <si>
+    <t>11.389</t>
+  </si>
+  <si>
+    <t>-0.485</t>
+  </si>
+  <si>
+    <t>-18.0643</t>
+  </si>
+  <si>
+    <t>-37.5888</t>
+  </si>
+  <si>
+    <t>-1204.5339</t>
+  </si>
+  <si>
+    <t>-22.3244</t>
+  </si>
+  <si>
+    <t>69636.4486+0.0909*B+0.0000*C+1.3589*D+1.8959*E-1.1786*F+0.0000*G-63.4661*H-1.0743*I-15.5020*J+23.2807*K-871.2577*L-29.3267*M</t>
+  </si>
+  <si>
+    <t>69636.4486</t>
+  </si>
+  <si>
+    <t>0.0909</t>
+  </si>
+  <si>
+    <t>1.3589</t>
+  </si>
+  <si>
+    <t>1.8959</t>
+  </si>
+  <si>
+    <t>-1.1786</t>
+  </si>
+  <si>
+    <t>-63.4661</t>
+  </si>
+  <si>
+    <t>-1.0743</t>
+  </si>
+  <si>
+    <t>-15.502</t>
+  </si>
+  <si>
+    <t>23.2807</t>
+  </si>
+  <si>
+    <t>-871.2577</t>
+  </si>
+  <si>
+    <t>-29.3267</t>
+  </si>
+  <si>
+    <t>14291.9704-0.1043*B+0.0000*C-13.1304*D+0.5297*E-1.9087*F+0.0000*G-14.3811*H+1.6913*I+21.9293*J+19.2133*K-708.3579*L-13.8705*M</t>
+  </si>
+  <si>
+    <t>14291.9704</t>
+  </si>
+  <si>
+    <t>-0.1043</t>
+  </si>
+  <si>
+    <t>-13.1304</t>
+  </si>
+  <si>
+    <t>0.5297</t>
+  </si>
+  <si>
+    <t>-1.9087</t>
+  </si>
+  <si>
+    <t>-14.3811</t>
+  </si>
+  <si>
+    <t>1.6913</t>
+  </si>
+  <si>
+    <t>21.9293</t>
+  </si>
+  <si>
+    <t>19.2133</t>
+  </si>
+  <si>
+    <t>-708.3579</t>
+  </si>
+  <si>
+    <t>-13.8705</t>
+  </si>
+  <si>
+    <t>47795.0591+0.3051*B+0.0000*C-11.1325*D-4.8783*E-0.7591*F+0.0000*G+52.8352*H-0.3508*I-22.6647*J-34.0136*K-105.3138*L-5.9195*M</t>
+  </si>
+  <si>
+    <t>47795.0591</t>
+  </si>
+  <si>
+    <t>0.3051</t>
+  </si>
+  <si>
+    <t>-11.1325</t>
+  </si>
+  <si>
+    <t>-4.8783</t>
+  </si>
+  <si>
+    <t>-0.7591</t>
+  </si>
+  <si>
+    <t>52.8352</t>
+  </si>
+  <si>
+    <t>-0.3508</t>
+  </si>
+  <si>
+    <t>-22.6647</t>
+  </si>
+  <si>
+    <t>-34.0136</t>
+  </si>
+  <si>
+    <t>-105.3138</t>
+  </si>
+  <si>
+    <t>-5.9195</t>
+  </si>
+  <si>
+    <t>14745.9125+0.1028*B+0.0000*C-4.6984*D-0.8390*E-1.5243*F+0.0000*G-92.5533*H-1.1539*I-13.3927*J-40.6719*K-207.8001*L-5.0140*M</t>
+  </si>
+  <si>
+    <t>14745.9125</t>
+  </si>
+  <si>
+    <t>0.1028</t>
+  </si>
+  <si>
+    <t>-4.6984</t>
+  </si>
+  <si>
+    <t>-0.839</t>
+  </si>
+  <si>
+    <t>-1.5243</t>
+  </si>
+  <si>
+    <t>-92.5533</t>
+  </si>
+  <si>
+    <t>-1.1539</t>
+  </si>
+  <si>
+    <t>-13.3927</t>
+  </si>
+  <si>
+    <t>-40.6719</t>
+  </si>
+  <si>
+    <t>-207.8001</t>
+  </si>
+  <si>
+    <t>-5.014</t>
+  </si>
+  <si>
+    <t>49288.7945+0.0387*B+0.0000*C-8.6680*D-2.3964*E-2.1601*F+0.0000*G-16.8613*H-1.8547*I+5.0710*J-4.4328*K-177.9781*L+3.0762*M</t>
+  </si>
+  <si>
+    <t>49288.7945</t>
+  </si>
+  <si>
+    <t>0.0387</t>
+  </si>
+  <si>
+    <t>-8.668</t>
+  </si>
+  <si>
+    <t>-2.3964</t>
+  </si>
+  <si>
+    <t>-2.1601</t>
+  </si>
+  <si>
+    <t>-16.8613</t>
+  </si>
+  <si>
+    <t>-1.8547</t>
+  </si>
+  <si>
+    <t>5.071</t>
+  </si>
+  <si>
+    <t>-4.4328</t>
+  </si>
+  <si>
+    <t>-177.9781</t>
+  </si>
+  <si>
+    <t>3.0762</t>
+  </si>
+  <si>
+    <t>18581.7276+0.0433*B+0.0000*C-10.3383*D-2.0209*E-0.7745*F+0.0000*G-1.5408*H-0.5894*I-2.1115*J-11.1430*K-821.7765*L+23.7968*M</t>
+  </si>
+  <si>
+    <t>18581.7276</t>
+  </si>
+  <si>
+    <t>0.0433</t>
+  </si>
+  <si>
+    <t>-10.3383</t>
+  </si>
+  <si>
+    <t>-2.0209</t>
+  </si>
+  <si>
+    <t>-0.7745</t>
+  </si>
+  <si>
+    <t>-1.5408</t>
+  </si>
+  <si>
+    <t>-0.5894</t>
+  </si>
+  <si>
+    <t>-2.1115</t>
+  </si>
+  <si>
+    <t>-11.143</t>
+  </si>
+  <si>
+    <t>-821.7765</t>
+  </si>
+  <si>
+    <t>23.7968</t>
+  </si>
+  <si>
+    <t>24271.9989+0.2561*B+0.0000*C-24.0472*D-1.1992*E-0.1786*F+0.0000*G+17.5844*H-1.3745*I+1.5332*J-51.5131*K-944.6687*L-15.2438*M</t>
+  </si>
+  <si>
+    <t>24271.9989</t>
+  </si>
+  <si>
+    <t>0.2561</t>
+  </si>
+  <si>
+    <t>-24.0472</t>
+  </si>
+  <si>
+    <t>-1.1992</t>
+  </si>
+  <si>
+    <t>-0.1786</t>
+  </si>
+  <si>
+    <t>17.5844</t>
+  </si>
+  <si>
+    <t>-1.3745</t>
+  </si>
+  <si>
+    <t>1.5332</t>
+  </si>
+  <si>
+    <t>-51.5131</t>
+  </si>
+  <si>
+    <t>-944.6687</t>
+  </si>
+  <si>
+    <t>-15.2438</t>
+  </si>
+  <si>
+    <t>64339.4135+0.0546*B+0.0000*C+16.3950*D-4.7929*E-1.1024*F+0.0000*G-16.8872*H-1.4761*I+5.6096*J-39.3042*K+32.7976*L-24.8589*M</t>
+  </si>
+  <si>
+    <t>64339.4135</t>
+  </si>
+  <si>
+    <t>0.0546</t>
+  </si>
+  <si>
+    <t>16.395</t>
+  </si>
+  <si>
+    <t>-4.7929</t>
+  </si>
+  <si>
+    <t>-1.1024</t>
+  </si>
+  <si>
+    <t>-16.8872</t>
+  </si>
+  <si>
+    <t>-1.4761</t>
+  </si>
+  <si>
+    <t>5.6096</t>
+  </si>
+  <si>
+    <t>-39.3042</t>
+  </si>
+  <si>
+    <t>32.7976</t>
+  </si>
+  <si>
+    <t>-24.8589</t>
+  </si>
+  <si>
+    <t>10568.7560+0.3127*B+0.0000*C-9.3640*D+0.2579*E-0.3485*F+0.0000*G-31.7201*H+2.2170*I+0.4165*J-18.5582*K-526.4145*L-28.2564*M</t>
+  </si>
+  <si>
+    <t>10568.756</t>
+  </si>
+  <si>
+    <t>0.3127</t>
+  </si>
+  <si>
+    <t>-9.364</t>
+  </si>
+  <si>
+    <t>0.2579</t>
+  </si>
+  <si>
+    <t>-0.3485</t>
+  </si>
+  <si>
+    <t>-31.7201</t>
+  </si>
+  <si>
+    <t>2.217</t>
+  </si>
+  <si>
+    <t>0.4165</t>
+  </si>
+  <si>
+    <t>-18.5582</t>
+  </si>
+  <si>
+    <t>-526.4145</t>
+  </si>
+  <si>
+    <t>-28.2564</t>
+  </si>
+  <si>
+    <t>28820.5662+0.1966*B+0.0000*C+9.1968*D+3.0696*E-0.0660*F+0.0000*G-86.0532*H+0.0313*I-12.9591*J-32.9259*K-1048.9552*L-11.6050*M</t>
+  </si>
+  <si>
+    <t>28820.5662</t>
+  </si>
+  <si>
+    <t>0.1966</t>
+  </si>
+  <si>
+    <t>9.1968</t>
+  </si>
+  <si>
+    <t>3.0696</t>
+  </si>
+  <si>
+    <t>-0.066</t>
+  </si>
+  <si>
+    <t>-86.0532</t>
+  </si>
+  <si>
+    <t>0.0313</t>
+  </si>
+  <si>
+    <t>-12.9591</t>
+  </si>
+  <si>
+    <t>-32.9259</t>
+  </si>
+  <si>
+    <t>-1048.9552</t>
+  </si>
+  <si>
+    <t>-11.605</t>
+  </si>
+  <si>
+    <t>1808.3285+0.1327*B+0.0000*C-21.4422*D-6.1614*E-0.5231*F+0.0000*G-102.8449*H-0.9857*I-28.6791*J-62.0132*K-412.9097*L-19.3306*M</t>
+  </si>
+  <si>
+    <t>1808.3285</t>
+  </si>
+  <si>
+    <t>0.1327</t>
+  </si>
+  <si>
+    <t>-21.4422</t>
+  </si>
+  <si>
+    <t>-6.1614</t>
+  </si>
+  <si>
+    <t>-0.5231</t>
+  </si>
+  <si>
+    <t>-102.8449</t>
+  </si>
+  <si>
+    <t>-0.9857</t>
+  </si>
+  <si>
+    <t>-28.6791</t>
+  </si>
+  <si>
+    <t>-62.0132</t>
+  </si>
+  <si>
+    <t>-412.9097</t>
+  </si>
+  <si>
+    <t>-19.3306</t>
+  </si>
+  <si>
+    <t>20009.4890+0.0489*B+0.0000*C-9.0479*D+2.3752*E-0.1200*F+0.0000*G+99.5800*H+1.7527*I+1.8247*J-16.6574*K-967.2216*L-22.3605*M</t>
+  </si>
+  <si>
+    <t>20009.489</t>
+  </si>
+  <si>
+    <t>0.0489</t>
+  </si>
+  <si>
+    <t>-9.0479</t>
+  </si>
+  <si>
+    <t>2.3752</t>
+  </si>
+  <si>
+    <t>-0.12</t>
+  </si>
+  <si>
+    <t>99.58</t>
+  </si>
+  <si>
+    <t>1.7527</t>
+  </si>
+  <si>
+    <t>1.8247</t>
+  </si>
+  <si>
+    <t>-16.6574</t>
+  </si>
+  <si>
+    <t>-967.2216</t>
+  </si>
+  <si>
+    <t>-22.3605</t>
+  </si>
+  <si>
+    <t>24297.6504+0.2957*B+0.0000*C-12.7561*D-0.6189*E-1.3716*F+0.0000*G-22.1327*H+0.4310*I+5.3947*J-9.6988*K-998.2584*L-17.5548*M</t>
+  </si>
+  <si>
+    <t>24297.6504</t>
+  </si>
+  <si>
+    <t>0.2957</t>
+  </si>
+  <si>
+    <t>-12.7561</t>
+  </si>
+  <si>
+    <t>-0.6189</t>
+  </si>
+  <si>
+    <t>-1.3716</t>
+  </si>
+  <si>
+    <t>-22.1327</t>
+  </si>
+  <si>
+    <t>0.431</t>
+  </si>
+  <si>
+    <t>5.3947</t>
+  </si>
+  <si>
+    <t>-9.6988</t>
+  </si>
+  <si>
+    <t>-998.2584</t>
+  </si>
+  <si>
+    <t>-17.5548</t>
+  </si>
+  <si>
+    <t>21525.8174+0.0061*B+0.0000*C+2.6988*D-0.1116*E+0.3873*F+0.0000*G-94.6535*H+0.0950*I-17.4978*J-22.1779*K-1460.9362*L-11.8724*M</t>
+  </si>
+  <si>
+    <t>21525.8174</t>
+  </si>
+  <si>
+    <t>0.0061</t>
+  </si>
+  <si>
+    <t>2.6988</t>
+  </si>
+  <si>
+    <t>-0.1116</t>
+  </si>
+  <si>
+    <t>0.3873</t>
+  </si>
+  <si>
+    <t>-94.6535</t>
+  </si>
+  <si>
+    <t>0.095</t>
+  </si>
+  <si>
+    <t>-17.4978</t>
+  </si>
+  <si>
+    <t>-22.1779</t>
+  </si>
+  <si>
+    <t>-1460.9362</t>
+  </si>
+  <si>
+    <t>-11.8724</t>
+  </si>
+  <si>
+    <t>-12962.7782-0.1454*B+0.0000*C+24.7725*D+0.6517*E+0.3390*F+0.0000*G-68.2594*H+1.2129*I-9.9272*J-28.5317*K-211.1597*L-10.4595*M</t>
+  </si>
+  <si>
+    <t>-12962.7782</t>
+  </si>
+  <si>
+    <t>-0.1454</t>
+  </si>
+  <si>
+    <t>24.7725</t>
+  </si>
+  <si>
+    <t>0.6517</t>
+  </si>
+  <si>
+    <t>0.339</t>
+  </si>
+  <si>
+    <t>-68.2594</t>
+  </si>
+  <si>
+    <t>1.2129</t>
+  </si>
+  <si>
+    <t>-9.9272</t>
+  </si>
+  <si>
+    <t>-28.5317</t>
+  </si>
+  <si>
+    <t>-211.1597</t>
+  </si>
+  <si>
+    <t>-10.4595</t>
+  </si>
+  <si>
+    <t>50214.7382-0.2577*B+0.0000*C-9.6430*D-1.4658*E-0.3249*F+0.0000*G-49.9611*H-0.3551*I-10.0067*J+4.7079*K-948.2168*L-17.9867*M</t>
+  </si>
+  <si>
+    <t>50214.7382</t>
+  </si>
+  <si>
+    <t>-0.2577</t>
+  </si>
+  <si>
+    <t>-9.643</t>
+  </si>
+  <si>
+    <t>-1.4658</t>
+  </si>
+  <si>
+    <t>-0.3249</t>
+  </si>
+  <si>
+    <t>-49.9611</t>
+  </si>
+  <si>
+    <t>-0.3551</t>
+  </si>
+  <si>
+    <t>-10.0067</t>
+  </si>
+  <si>
+    <t>4.7079</t>
+  </si>
+  <si>
+    <t>-948.2168</t>
+  </si>
+  <si>
+    <t>-17.9867</t>
+  </si>
+  <si>
+    <t>22742.0540+0.0333*B+0.0000*C+1.7783*D-3.0168*E-0.3290*F+0.0000*G-35.7285*H-1.3749*I-25.6177*J-12.3739*K-664.9859*L-13.3593*M</t>
+  </si>
+  <si>
+    <t>22742.054</t>
+  </si>
+  <si>
+    <t>0.0333</t>
+  </si>
+  <si>
+    <t>1.7783</t>
+  </si>
+  <si>
+    <t>-3.0168</t>
+  </si>
+  <si>
+    <t>-0.329</t>
+  </si>
+  <si>
+    <t>-35.7285</t>
+  </si>
+  <si>
+    <t>-1.3749</t>
+  </si>
+  <si>
+    <t>-25.6177</t>
+  </si>
+  <si>
+    <t>-12.3739</t>
+  </si>
+  <si>
+    <t>-664.9859</t>
+  </si>
+  <si>
+    <t>-13.3593</t>
+  </si>
+  <si>
+    <t>12074.8443+0.3873*B+0.0000*C-13.0124*D-0.6857*E-0.7907*F+0.0000*G-128.4303*H-0.1444*I-21.8992*J+0.9904*K-21.2392*L-7.1937*M</t>
+  </si>
+  <si>
+    <t>12074.8443</t>
+  </si>
+  <si>
+    <t>-13.0124</t>
+  </si>
+  <si>
+    <t>-0.6857</t>
+  </si>
+  <si>
+    <t>-0.7907</t>
+  </si>
+  <si>
+    <t>-128.4303</t>
+  </si>
+  <si>
+    <t>-0.1444</t>
+  </si>
+  <si>
+    <t>-21.8992</t>
+  </si>
+  <si>
+    <t>0.9904</t>
+  </si>
+  <si>
+    <t>-21.2392</t>
+  </si>
+  <si>
+    <t>-7.1937</t>
+  </si>
+  <si>
+    <t>33450.4052-0.0535*B+0.0000*C+6.7999*D+1.2108*E+0.4686*F+0.0000*G+34.8687*H-2.0963*I-2.4845*J-71.7664*K+78.5092*L-21.1622*M</t>
+  </si>
+  <si>
+    <t>33450.4052</t>
+  </si>
+  <si>
+    <t>-0.0535</t>
+  </si>
+  <si>
+    <t>6.7999</t>
+  </si>
+  <si>
+    <t>1.2108</t>
+  </si>
+  <si>
+    <t>0.4686</t>
+  </si>
+  <si>
+    <t>34.8687</t>
+  </si>
+  <si>
+    <t>-2.0963</t>
+  </si>
+  <si>
+    <t>-2.4845</t>
+  </si>
+  <si>
+    <t>-71.7664</t>
+  </si>
+  <si>
+    <t>78.5092</t>
+  </si>
+  <si>
+    <t>-21.1622</t>
+  </si>
+  <si>
+    <t>28017.7628-0.0562*B+0.0000*C+3.4301*D+0.7380*E-1.2465*F+0.0000*G-53.3495*H-0.6398*I+2.8025*J-21.6137*K-691.6981*L+18.8937*M</t>
+  </si>
+  <si>
+    <t>28017.7628</t>
+  </si>
+  <si>
+    <t>-0.0562</t>
+  </si>
+  <si>
+    <t>3.4301</t>
+  </si>
+  <si>
+    <t>0.738</t>
+  </si>
+  <si>
+    <t>-1.2465</t>
+  </si>
+  <si>
+    <t>-53.3495</t>
+  </si>
+  <si>
+    <t>-0.6398</t>
+  </si>
+  <si>
+    <t>2.8025</t>
+  </si>
+  <si>
+    <t>-21.6137</t>
+  </si>
+  <si>
+    <t>-691.6981</t>
+  </si>
+  <si>
+    <t>18.8937</t>
+  </si>
+  <si>
+    <t>-38232.5076+0.1967*B+0.0000*C-0.0778*D+0.8848*E+0.3095*F+0.0000*G+34.3113*H-1.3737*I+7.5634*J-5.3134*K-967.4794*L-0.6000*M</t>
+  </si>
+  <si>
+    <t>-38232.5076</t>
+  </si>
+  <si>
+    <t>0.1967</t>
+  </si>
+  <si>
+    <t>-0.0778</t>
+  </si>
+  <si>
+    <t>0.8848</t>
+  </si>
+  <si>
+    <t>0.3095</t>
+  </si>
+  <si>
+    <t>34.3113</t>
+  </si>
+  <si>
+    <t>-1.3737</t>
+  </si>
+  <si>
+    <t>7.5634</t>
+  </si>
+  <si>
+    <t>-5.3134</t>
+  </si>
+  <si>
+    <t>-967.4794</t>
+  </si>
+  <si>
+    <t>-0.6</t>
+  </si>
+  <si>
+    <t>-13432.7281+0.2175*B+0.0000*C-2.6006*D+2.0362*E-0.9117*F+0.0000*G-47.5388*H-0.6830*I-10.9280*J-49.4663*K-580.0457*L-22.8580*M</t>
+  </si>
+  <si>
+    <t>-13432.7281</t>
+  </si>
+  <si>
+    <t>0.2175</t>
+  </si>
+  <si>
+    <t>-2.6006</t>
+  </si>
+  <si>
+    <t>2.0362</t>
+  </si>
+  <si>
+    <t>-0.9117</t>
+  </si>
+  <si>
+    <t>-47.5388</t>
+  </si>
+  <si>
+    <t>-0.683</t>
+  </si>
+  <si>
+    <t>-10.928</t>
+  </si>
+  <si>
+    <t>-49.4663</t>
+  </si>
+  <si>
+    <t>-580.0457</t>
+  </si>
+  <si>
+    <t>-22.858</t>
+  </si>
+  <si>
+    <t>40915.2664+0.2517*B+0.0000*C-15.6599*D-0.5381*E-0.2812*F+0.0000*G-66.1294*H+1.4755*I-6.2161*J-5.9172*K-844.6452*L-3.0332*M</t>
+  </si>
+  <si>
+    <t>40915.2664</t>
+  </si>
+  <si>
+    <t>0.2517</t>
+  </si>
+  <si>
+    <t>-15.6599</t>
+  </si>
+  <si>
+    <t>-0.5381</t>
+  </si>
+  <si>
+    <t>-0.2812</t>
+  </si>
+  <si>
+    <t>-66.1294</t>
+  </si>
+  <si>
+    <t>1.4755</t>
+  </si>
+  <si>
+    <t>-6.2161</t>
+  </si>
+  <si>
+    <t>-5.9172</t>
+  </si>
+  <si>
+    <t>-844.6452</t>
+  </si>
+  <si>
+    <t>-3.0332</t>
+  </si>
+  <si>
+    <t>88852.9454-0.0867*B+0.0000*C+3.1892*D+0.0618*E+0.0518*F+0.0000*G-27.8013*H-2.4347*I-18.3249*J-4.0550*K-1676.7349*L-3.2406*M</t>
+  </si>
+  <si>
+    <t>88852.9454</t>
+  </si>
+  <si>
+    <t>-0.0867</t>
+  </si>
+  <si>
+    <t>3.1892</t>
+  </si>
+  <si>
+    <t>0.0618</t>
+  </si>
+  <si>
+    <t>0.0518</t>
+  </si>
+  <si>
+    <t>-27.8013</t>
+  </si>
+  <si>
+    <t>-2.4347</t>
+  </si>
+  <si>
+    <t>-18.3249</t>
+  </si>
+  <si>
+    <t>-4.055</t>
+  </si>
+  <si>
+    <t>-1676.7349</t>
+  </si>
+  <si>
+    <t>-3.2406</t>
+  </si>
+  <si>
+    <t>27724.0446+0.1563*B+0.0000*C+5.7649*D-0.6505*E+0.1006*F+0.0000*G-82.9332*H+0.0292*I-5.0200*J-39.0566*K-697.3174*L+14.9213*M</t>
+  </si>
+  <si>
+    <t>27724.0446</t>
+  </si>
+  <si>
+    <t>0.1563</t>
+  </si>
+  <si>
+    <t>5.7649</t>
+  </si>
+  <si>
+    <t>-0.6505</t>
+  </si>
+  <si>
+    <t>0.1006</t>
+  </si>
+  <si>
+    <t>-82.9332</t>
+  </si>
+  <si>
+    <t>0.0292</t>
+  </si>
+  <si>
+    <t>-5.02</t>
+  </si>
+  <si>
+    <t>-39.0566</t>
+  </si>
+  <si>
+    <t>-697.3174</t>
+  </si>
+  <si>
+    <t>14.9213</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t>88</t>
+  </si>
+  <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>120</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
@@ -2054,6 +5175,10 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2073,10 +5198,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2084,12 +5213,17 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="2">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="text_format" xfId="2" xr:uid="{8BF6EAAF-C1FA-4734-ADF1-D4A756A27805}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{C0E996C0-0040-4843-BFF0-532D82134C01}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -2391,7 +5525,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O121"/>
   <sheetFormatPr defaultRowHeight="14.6"/>
   <cols>
     <col min="3" max="15" width="9.23046875" style="2"/>
@@ -4324,8 +7458,3768 @@
         <v>485</v>
       </c>
     </row>
+    <row r="42" spans="1:15">
+      <c r="A42" t="s">
+        <v>1485</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="E42" s="2">
+        <v>0</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="I42" s="2">
+        <v>0</v>
+      </c>
+      <c r="J42" s="4" t="s">
+        <v>533</v>
+      </c>
+      <c r="K42" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="L42" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="M42" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="N42" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="O42" s="4" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15">
+      <c r="A43" t="s">
+        <v>1486</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="E43" s="2">
+        <v>0</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="I43" s="2">
+        <v>0</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="K43" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="L43" s="4" t="s">
+        <v>547</v>
+      </c>
+      <c r="M43" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="N43" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="O43" s="4" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15">
+      <c r="A44" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="E44" s="2">
+        <v>0</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="I44" s="2">
+        <v>0</v>
+      </c>
+      <c r="J44" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="K44" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="L44" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="M44" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="N44" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="O44" s="4" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15">
+      <c r="A45" t="s">
+        <v>1488</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="E45" s="2">
+        <v>0</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="I45" s="2">
+        <v>0</v>
+      </c>
+      <c r="J45" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="L45" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="M45" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="N45" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="O45" s="4" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15">
+      <c r="A46" t="s">
+        <v>1489</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="E46" s="2">
+        <v>0</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="I46" s="2">
+        <v>0</v>
+      </c>
+      <c r="J46" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="K46" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="L46" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="M46" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="N46" s="4" t="s">
+        <v>585</v>
+      </c>
+      <c r="O46" s="4" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15">
+      <c r="A47" t="s">
+        <v>1490</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="E47" s="2">
+        <v>0</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>590</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="I47" s="2">
+        <v>0</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="K47" s="4" t="s">
+        <v>594</v>
+      </c>
+      <c r="L47" s="4" t="s">
+        <v>595</v>
+      </c>
+      <c r="M47" s="4" t="s">
+        <v>596</v>
+      </c>
+      <c r="N47" s="4" t="s">
+        <v>597</v>
+      </c>
+      <c r="O47" s="4" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15">
+      <c r="A48" t="s">
+        <v>1491</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="E48" s="2">
+        <v>0</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="I48" s="2">
+        <v>0</v>
+      </c>
+      <c r="J48" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="K48" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="L48" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="M48" s="4" t="s">
+        <v>608</v>
+      </c>
+      <c r="N48" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="O48" s="4" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15">
+      <c r="A49" t="s">
+        <v>1492</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="E49" s="2">
+        <v>0</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="I49" s="2">
+        <v>0</v>
+      </c>
+      <c r="J49" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="K49" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="L49" s="4" t="s">
+        <v>619</v>
+      </c>
+      <c r="M49" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="N49" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="O49" s="4" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15">
+      <c r="A50" t="s">
+        <v>1493</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>625</v>
+      </c>
+      <c r="E50" s="2">
+        <v>0</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="I50" s="2">
+        <v>0</v>
+      </c>
+      <c r="J50" s="4" t="s">
+        <v>629</v>
+      </c>
+      <c r="K50" s="4" t="s">
+        <v>630</v>
+      </c>
+      <c r="L50" s="4" t="s">
+        <v>631</v>
+      </c>
+      <c r="M50" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="N50" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="O50" s="4" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15">
+      <c r="A51" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>635</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>636</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>637</v>
+      </c>
+      <c r="E51" s="2">
+        <v>0</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>640</v>
+      </c>
+      <c r="I51" s="2">
+        <v>0</v>
+      </c>
+      <c r="J51" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="K51" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="L51" s="4" t="s">
+        <v>643</v>
+      </c>
+      <c r="M51" s="4" t="s">
+        <v>644</v>
+      </c>
+      <c r="N51" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="O51" s="4" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15">
+      <c r="A52" t="s">
+        <v>1495</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>647</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>648</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>649</v>
+      </c>
+      <c r="E52" s="2">
+        <v>0</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="I52" s="2">
+        <v>0</v>
+      </c>
+      <c r="J52" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="K52" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="L52" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="M52" s="4" t="s">
+        <v>656</v>
+      </c>
+      <c r="N52" s="4" t="s">
+        <v>657</v>
+      </c>
+      <c r="O52" s="4" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15">
+      <c r="A53" t="s">
+        <v>1496</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>659</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="E53" s="2">
+        <v>0</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>662</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>663</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>664</v>
+      </c>
+      <c r="I53" s="2">
+        <v>0</v>
+      </c>
+      <c r="J53" s="4" t="s">
+        <v>665</v>
+      </c>
+      <c r="K53" s="4" t="s">
+        <v>666</v>
+      </c>
+      <c r="L53" s="4" t="s">
+        <v>667</v>
+      </c>
+      <c r="M53" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="N53" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="O53" s="4" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15">
+      <c r="A54" t="s">
+        <v>1497</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>672</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="E54" s="2">
+        <v>0</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>675</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>676</v>
+      </c>
+      <c r="I54" s="2">
+        <v>0</v>
+      </c>
+      <c r="J54" s="4" t="s">
+        <v>677</v>
+      </c>
+      <c r="K54" s="4" t="s">
+        <v>678</v>
+      </c>
+      <c r="L54" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="M54" s="4" t="s">
+        <v>680</v>
+      </c>
+      <c r="N54" s="4" t="s">
+        <v>681</v>
+      </c>
+      <c r="O54" s="4" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15">
+      <c r="A55" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>683</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>684</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>685</v>
+      </c>
+      <c r="E55" s="2">
+        <v>0</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>687</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>688</v>
+      </c>
+      <c r="I55" s="2">
+        <v>0</v>
+      </c>
+      <c r="J55" s="4" t="s">
+        <v>689</v>
+      </c>
+      <c r="K55" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="L55" s="4" t="s">
+        <v>691</v>
+      </c>
+      <c r="M55" s="4" t="s">
+        <v>692</v>
+      </c>
+      <c r="N55" s="4" t="s">
+        <v>693</v>
+      </c>
+      <c r="O55" s="4" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15">
+      <c r="A56" t="s">
+        <v>1499</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>696</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>697</v>
+      </c>
+      <c r="E56" s="2">
+        <v>0</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>698</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>699</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>700</v>
+      </c>
+      <c r="I56" s="2">
+        <v>0</v>
+      </c>
+      <c r="J56" s="4" t="s">
+        <v>701</v>
+      </c>
+      <c r="K56" s="4" t="s">
+        <v>702</v>
+      </c>
+      <c r="L56" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="M56" s="4" t="s">
+        <v>704</v>
+      </c>
+      <c r="N56" s="4" t="s">
+        <v>705</v>
+      </c>
+      <c r="O56" s="4" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15">
+      <c r="A57" t="s">
+        <v>1500</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>707</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>708</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>709</v>
+      </c>
+      <c r="E57" s="2">
+        <v>0</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>710</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>711</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="I57" s="2">
+        <v>0</v>
+      </c>
+      <c r="J57" s="4" t="s">
+        <v>713</v>
+      </c>
+      <c r="K57" s="4" t="s">
+        <v>714</v>
+      </c>
+      <c r="L57" s="4" t="s">
+        <v>715</v>
+      </c>
+      <c r="M57" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="N57" s="4" t="s">
+        <v>717</v>
+      </c>
+      <c r="O57" s="4" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15">
+      <c r="A58" t="s">
+        <v>1501</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>719</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>720</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="E58" s="2">
+        <v>0</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>723</v>
+      </c>
+      <c r="H58" s="4" t="s">
+        <v>724</v>
+      </c>
+      <c r="I58" s="2">
+        <v>0</v>
+      </c>
+      <c r="J58" s="4" t="s">
+        <v>725</v>
+      </c>
+      <c r="K58" s="4" t="s">
+        <v>726</v>
+      </c>
+      <c r="L58" s="4" t="s">
+        <v>727</v>
+      </c>
+      <c r="M58" s="4" t="s">
+        <v>728</v>
+      </c>
+      <c r="N58" s="4" t="s">
+        <v>729</v>
+      </c>
+      <c r="O58" s="4" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15">
+      <c r="A59" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>731</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>732</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>733</v>
+      </c>
+      <c r="E59" s="2">
+        <v>0</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>734</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>735</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>736</v>
+      </c>
+      <c r="I59" s="2">
+        <v>0</v>
+      </c>
+      <c r="J59" s="4" t="s">
+        <v>737</v>
+      </c>
+      <c r="K59" s="4" t="s">
+        <v>738</v>
+      </c>
+      <c r="L59" s="4" t="s">
+        <v>739</v>
+      </c>
+      <c r="M59" s="4" t="s">
+        <v>740</v>
+      </c>
+      <c r="N59" s="4" t="s">
+        <v>741</v>
+      </c>
+      <c r="O59" s="4" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15">
+      <c r="A60" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>743</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>744</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="E60" s="2">
+        <v>0</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>746</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>748</v>
+      </c>
+      <c r="I60" s="2">
+        <v>0</v>
+      </c>
+      <c r="J60" s="4" t="s">
+        <v>749</v>
+      </c>
+      <c r="K60" s="4" t="s">
+        <v>750</v>
+      </c>
+      <c r="L60" s="4" t="s">
+        <v>751</v>
+      </c>
+      <c r="M60" s="4" t="s">
+        <v>752</v>
+      </c>
+      <c r="N60" s="4" t="s">
+        <v>753</v>
+      </c>
+      <c r="O60" s="4" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15">
+      <c r="A61" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>756</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>757</v>
+      </c>
+      <c r="E61" s="2">
+        <v>0</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>758</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>759</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>760</v>
+      </c>
+      <c r="I61" s="2">
+        <v>0</v>
+      </c>
+      <c r="J61" s="4" t="s">
+        <v>761</v>
+      </c>
+      <c r="K61" s="4" t="s">
+        <v>762</v>
+      </c>
+      <c r="L61" s="4" t="s">
+        <v>763</v>
+      </c>
+      <c r="M61" s="4" t="s">
+        <v>764</v>
+      </c>
+      <c r="N61" s="4" t="s">
+        <v>765</v>
+      </c>
+      <c r="O61" s="4" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15">
+      <c r="A62" t="s">
+        <v>1505</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>768</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>769</v>
+      </c>
+      <c r="E62" s="2">
+        <v>0</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>770</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>771</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="I62" s="2">
+        <v>0</v>
+      </c>
+      <c r="J62" s="4" t="s">
+        <v>773</v>
+      </c>
+      <c r="K62" s="4" t="s">
+        <v>774</v>
+      </c>
+      <c r="L62" s="4" t="s">
+        <v>775</v>
+      </c>
+      <c r="M62" s="4" t="s">
+        <v>776</v>
+      </c>
+      <c r="N62" s="4" t="s">
+        <v>777</v>
+      </c>
+      <c r="O62" s="4" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15">
+      <c r="A63" t="s">
+        <v>1506</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>779</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>780</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>781</v>
+      </c>
+      <c r="E63" s="2">
+        <v>0</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>782</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>783</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>784</v>
+      </c>
+      <c r="I63" s="2">
+        <v>0</v>
+      </c>
+      <c r="J63" s="4" t="s">
+        <v>785</v>
+      </c>
+      <c r="K63" s="4" t="s">
+        <v>786</v>
+      </c>
+      <c r="L63" s="4" t="s">
+        <v>787</v>
+      </c>
+      <c r="M63" s="4" t="s">
+        <v>788</v>
+      </c>
+      <c r="N63" s="4" t="s">
+        <v>789</v>
+      </c>
+      <c r="O63" s="4" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15">
+      <c r="A64" t="s">
+        <v>1507</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>791</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>792</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>793</v>
+      </c>
+      <c r="E64" s="2">
+        <v>0</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>794</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>795</v>
+      </c>
+      <c r="H64" s="4" t="s">
+        <v>796</v>
+      </c>
+      <c r="I64" s="2">
+        <v>0</v>
+      </c>
+      <c r="J64" s="4" t="s">
+        <v>797</v>
+      </c>
+      <c r="K64" s="4" t="s">
+        <v>798</v>
+      </c>
+      <c r="L64" s="4" t="s">
+        <v>799</v>
+      </c>
+      <c r="M64" s="4" t="s">
+        <v>800</v>
+      </c>
+      <c r="N64" s="4" t="s">
+        <v>801</v>
+      </c>
+      <c r="O64" s="4" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15">
+      <c r="A65" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>803</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>804</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>805</v>
+      </c>
+      <c r="E65" s="2">
+        <v>0</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>806</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>807</v>
+      </c>
+      <c r="H65" s="4" t="s">
+        <v>808</v>
+      </c>
+      <c r="I65" s="2">
+        <v>0</v>
+      </c>
+      <c r="J65" s="4" t="s">
+        <v>809</v>
+      </c>
+      <c r="K65" s="4" t="s">
+        <v>810</v>
+      </c>
+      <c r="L65" s="4" t="s">
+        <v>811</v>
+      </c>
+      <c r="M65" s="4" t="s">
+        <v>812</v>
+      </c>
+      <c r="N65" s="4" t="s">
+        <v>813</v>
+      </c>
+      <c r="O65" s="4" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15">
+      <c r="A66" t="s">
+        <v>1509</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>815</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>816</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>817</v>
+      </c>
+      <c r="E66" s="2">
+        <v>0</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>818</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>819</v>
+      </c>
+      <c r="H66" s="4" t="s">
+        <v>820</v>
+      </c>
+      <c r="I66" s="2">
+        <v>0</v>
+      </c>
+      <c r="J66" s="4" t="s">
+        <v>821</v>
+      </c>
+      <c r="K66" s="4" t="s">
+        <v>822</v>
+      </c>
+      <c r="L66" s="4" t="s">
+        <v>823</v>
+      </c>
+      <c r="M66" s="4" t="s">
+        <v>824</v>
+      </c>
+      <c r="N66" s="4" t="s">
+        <v>825</v>
+      </c>
+      <c r="O66" s="4" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15">
+      <c r="A67" t="s">
+        <v>1510</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>827</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>828</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>829</v>
+      </c>
+      <c r="E67" s="2">
+        <v>0</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>830</v>
+      </c>
+      <c r="G67" s="4" t="s">
+        <v>831</v>
+      </c>
+      <c r="H67" s="4" t="s">
+        <v>832</v>
+      </c>
+      <c r="I67" s="2">
+        <v>0</v>
+      </c>
+      <c r="J67" s="4" t="s">
+        <v>833</v>
+      </c>
+      <c r="K67" s="4" t="s">
+        <v>834</v>
+      </c>
+      <c r="L67" s="4" t="s">
+        <v>835</v>
+      </c>
+      <c r="M67" s="4" t="s">
+        <v>836</v>
+      </c>
+      <c r="N67" s="4" t="s">
+        <v>837</v>
+      </c>
+      <c r="O67" s="4" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15">
+      <c r="A68" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>839</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>840</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>841</v>
+      </c>
+      <c r="E68" s="2">
+        <v>0</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>842</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>843</v>
+      </c>
+      <c r="H68" s="4" t="s">
+        <v>844</v>
+      </c>
+      <c r="I68" s="2">
+        <v>0</v>
+      </c>
+      <c r="J68" s="4" t="s">
+        <v>845</v>
+      </c>
+      <c r="K68" s="4" t="s">
+        <v>846</v>
+      </c>
+      <c r="L68" s="4" t="s">
+        <v>847</v>
+      </c>
+      <c r="M68" s="4" t="s">
+        <v>848</v>
+      </c>
+      <c r="N68" s="4" t="s">
+        <v>849</v>
+      </c>
+      <c r="O68" s="4" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15">
+      <c r="A69" t="s">
+        <v>1512</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>851</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>852</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>853</v>
+      </c>
+      <c r="E69" s="2">
+        <v>0</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>854</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>855</v>
+      </c>
+      <c r="H69" s="4" t="s">
+        <v>856</v>
+      </c>
+      <c r="I69" s="2">
+        <v>0</v>
+      </c>
+      <c r="J69" s="4" t="s">
+        <v>857</v>
+      </c>
+      <c r="K69" s="4" t="s">
+        <v>858</v>
+      </c>
+      <c r="L69" s="4" t="s">
+        <v>859</v>
+      </c>
+      <c r="M69" s="4" t="s">
+        <v>860</v>
+      </c>
+      <c r="N69" s="4" t="s">
+        <v>861</v>
+      </c>
+      <c r="O69" s="4" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15">
+      <c r="A70" t="s">
+        <v>1513</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>863</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>864</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>865</v>
+      </c>
+      <c r="E70" s="2">
+        <v>0</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>866</v>
+      </c>
+      <c r="G70" s="4" t="s">
+        <v>867</v>
+      </c>
+      <c r="H70" s="4" t="s">
+        <v>868</v>
+      </c>
+      <c r="I70" s="2">
+        <v>0</v>
+      </c>
+      <c r="J70" s="4" t="s">
+        <v>869</v>
+      </c>
+      <c r="K70" s="4" t="s">
+        <v>870</v>
+      </c>
+      <c r="L70" s="4" t="s">
+        <v>871</v>
+      </c>
+      <c r="M70" s="4" t="s">
+        <v>872</v>
+      </c>
+      <c r="N70" s="4" t="s">
+        <v>873</v>
+      </c>
+      <c r="O70" s="4" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15">
+      <c r="A71" t="s">
+        <v>1514</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>875</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>876</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>877</v>
+      </c>
+      <c r="E71" s="2">
+        <v>0</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>878</v>
+      </c>
+      <c r="G71" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="H71" s="4" t="s">
+        <v>880</v>
+      </c>
+      <c r="I71" s="2">
+        <v>0</v>
+      </c>
+      <c r="J71" s="4" t="s">
+        <v>881</v>
+      </c>
+      <c r="K71" s="4" t="s">
+        <v>882</v>
+      </c>
+      <c r="L71" s="4" t="s">
+        <v>883</v>
+      </c>
+      <c r="M71" s="4" t="s">
+        <v>884</v>
+      </c>
+      <c r="N71" s="4" t="s">
+        <v>885</v>
+      </c>
+      <c r="O71" s="4" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15">
+      <c r="A72" t="s">
+        <v>1515</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>888</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="E72" s="2">
+        <v>0</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>890</v>
+      </c>
+      <c r="G72" s="4" t="s">
+        <v>891</v>
+      </c>
+      <c r="H72" s="4" t="s">
+        <v>892</v>
+      </c>
+      <c r="I72" s="2">
+        <v>0</v>
+      </c>
+      <c r="J72" s="4" t="s">
+        <v>893</v>
+      </c>
+      <c r="K72" s="4" t="s">
+        <v>894</v>
+      </c>
+      <c r="L72" s="4" t="s">
+        <v>895</v>
+      </c>
+      <c r="M72" s="4" t="s">
+        <v>896</v>
+      </c>
+      <c r="N72" s="4" t="s">
+        <v>897</v>
+      </c>
+      <c r="O72" s="4" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15">
+      <c r="A73" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>899</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>900</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>901</v>
+      </c>
+      <c r="E73" s="2">
+        <v>0</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>902</v>
+      </c>
+      <c r="G73" s="4" t="s">
+        <v>903</v>
+      </c>
+      <c r="H73" s="4" t="s">
+        <v>904</v>
+      </c>
+      <c r="I73" s="2">
+        <v>0</v>
+      </c>
+      <c r="J73" s="4" t="s">
+        <v>905</v>
+      </c>
+      <c r="K73" s="4" t="s">
+        <v>906</v>
+      </c>
+      <c r="L73" s="4" t="s">
+        <v>907</v>
+      </c>
+      <c r="M73" s="4" t="s">
+        <v>908</v>
+      </c>
+      <c r="N73" s="4" t="s">
+        <v>909</v>
+      </c>
+      <c r="O73" s="4" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15">
+      <c r="A74" t="s">
+        <v>1517</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>911</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="E74" s="2">
+        <v>0</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>914</v>
+      </c>
+      <c r="G74" s="4" t="s">
+        <v>915</v>
+      </c>
+      <c r="H74" s="4" t="s">
+        <v>916</v>
+      </c>
+      <c r="I74" s="2">
+        <v>0</v>
+      </c>
+      <c r="J74" s="4" t="s">
+        <v>917</v>
+      </c>
+      <c r="K74" s="4" t="s">
+        <v>918</v>
+      </c>
+      <c r="L74" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="M74" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="N74" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="O74" s="4" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15">
+      <c r="A75" t="s">
+        <v>1518</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>923</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>924</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>925</v>
+      </c>
+      <c r="E75" s="2">
+        <v>0</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>926</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>927</v>
+      </c>
+      <c r="H75" s="4" t="s">
+        <v>928</v>
+      </c>
+      <c r="I75" s="2">
+        <v>0</v>
+      </c>
+      <c r="J75" s="4" t="s">
+        <v>929</v>
+      </c>
+      <c r="K75" s="4" t="s">
+        <v>930</v>
+      </c>
+      <c r="L75" s="4" t="s">
+        <v>931</v>
+      </c>
+      <c r="M75" s="4" t="s">
+        <v>932</v>
+      </c>
+      <c r="N75" s="4" t="s">
+        <v>933</v>
+      </c>
+      <c r="O75" s="4" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15">
+      <c r="A76" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>935</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>936</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>937</v>
+      </c>
+      <c r="E76" s="2">
+        <v>0</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>938</v>
+      </c>
+      <c r="G76" s="4" t="s">
+        <v>939</v>
+      </c>
+      <c r="H76" s="4" t="s">
+        <v>940</v>
+      </c>
+      <c r="I76" s="2">
+        <v>0</v>
+      </c>
+      <c r="J76" s="4" t="s">
+        <v>941</v>
+      </c>
+      <c r="K76" s="4" t="s">
+        <v>942</v>
+      </c>
+      <c r="L76" s="4" t="s">
+        <v>943</v>
+      </c>
+      <c r="M76" s="4" t="s">
+        <v>944</v>
+      </c>
+      <c r="N76" s="4" t="s">
+        <v>945</v>
+      </c>
+      <c r="O76" s="4" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15">
+      <c r="A77" t="s">
+        <v>1520</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>949</v>
+      </c>
+      <c r="E77" s="2">
+        <v>0</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>950</v>
+      </c>
+      <c r="G77" s="4" t="s">
+        <v>951</v>
+      </c>
+      <c r="H77" s="4" t="s">
+        <v>952</v>
+      </c>
+      <c r="I77" s="2">
+        <v>0</v>
+      </c>
+      <c r="J77" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="K77" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="L77" s="4" t="s">
+        <v>955</v>
+      </c>
+      <c r="M77" s="4" t="s">
+        <v>956</v>
+      </c>
+      <c r="N77" s="4" t="s">
+        <v>957</v>
+      </c>
+      <c r="O77" s="4" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15">
+      <c r="A78" t="s">
+        <v>1521</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>959</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>960</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>961</v>
+      </c>
+      <c r="E78" s="2">
+        <v>0</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>962</v>
+      </c>
+      <c r="G78" s="4" t="s">
+        <v>963</v>
+      </c>
+      <c r="H78" s="4" t="s">
+        <v>964</v>
+      </c>
+      <c r="I78" s="2">
+        <v>0</v>
+      </c>
+      <c r="J78" s="4" t="s">
+        <v>965</v>
+      </c>
+      <c r="K78" s="4" t="s">
+        <v>966</v>
+      </c>
+      <c r="L78" s="4" t="s">
+        <v>967</v>
+      </c>
+      <c r="M78" s="4" t="s">
+        <v>968</v>
+      </c>
+      <c r="N78" s="4" t="s">
+        <v>969</v>
+      </c>
+      <c r="O78" s="4" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15">
+      <c r="A79" t="s">
+        <v>1522</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>971</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>972</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>973</v>
+      </c>
+      <c r="E79" s="2">
+        <v>0</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>974</v>
+      </c>
+      <c r="G79" s="4" t="s">
+        <v>975</v>
+      </c>
+      <c r="H79" s="4" t="s">
+        <v>976</v>
+      </c>
+      <c r="I79" s="2">
+        <v>0</v>
+      </c>
+      <c r="J79" s="4" t="s">
+        <v>977</v>
+      </c>
+      <c r="K79" s="4" t="s">
+        <v>978</v>
+      </c>
+      <c r="L79" s="4" t="s">
+        <v>979</v>
+      </c>
+      <c r="M79" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="N79" s="4" t="s">
+        <v>981</v>
+      </c>
+      <c r="O79" s="4" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15">
+      <c r="A80" t="s">
+        <v>1523</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>983</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>984</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>985</v>
+      </c>
+      <c r="E80" s="2">
+        <v>0</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>986</v>
+      </c>
+      <c r="G80" s="4" t="s">
+        <v>987</v>
+      </c>
+      <c r="H80" s="4" t="s">
+        <v>988</v>
+      </c>
+      <c r="I80" s="2">
+        <v>0</v>
+      </c>
+      <c r="J80" s="4" t="s">
+        <v>989</v>
+      </c>
+      <c r="K80" s="4" t="s">
+        <v>990</v>
+      </c>
+      <c r="L80" s="4" t="s">
+        <v>991</v>
+      </c>
+      <c r="M80" s="4" t="s">
+        <v>992</v>
+      </c>
+      <c r="N80" s="4" t="s">
+        <v>993</v>
+      </c>
+      <c r="O80" s="4" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15">
+      <c r="A81" t="s">
+        <v>1524</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>995</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>996</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>997</v>
+      </c>
+      <c r="E81" s="2">
+        <v>0</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>998</v>
+      </c>
+      <c r="G81" s="4" t="s">
+        <v>999</v>
+      </c>
+      <c r="H81" s="4" t="s">
+        <v>1000</v>
+      </c>
+      <c r="I81" s="2">
+        <v>0</v>
+      </c>
+      <c r="J81" s="4" t="s">
+        <v>1001</v>
+      </c>
+      <c r="K81" s="4" t="s">
+        <v>1002</v>
+      </c>
+      <c r="L81" s="4" t="s">
+        <v>1003</v>
+      </c>
+      <c r="M81" s="4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="N81" s="4" t="s">
+        <v>1005</v>
+      </c>
+      <c r="O81" s="4" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15">
+      <c r="A82" t="s">
+        <v>1525</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E82" s="2">
+        <v>0</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="G82" s="4" t="s">
+        <v>1011</v>
+      </c>
+      <c r="H82" s="4" t="s">
+        <v>1012</v>
+      </c>
+      <c r="I82" s="2">
+        <v>0</v>
+      </c>
+      <c r="J82" s="4" t="s">
+        <v>1013</v>
+      </c>
+      <c r="K82" s="4" t="s">
+        <v>1014</v>
+      </c>
+      <c r="L82" s="4" t="s">
+        <v>1015</v>
+      </c>
+      <c r="M82" s="4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="N82" s="4" t="s">
+        <v>1017</v>
+      </c>
+      <c r="O82" s="4" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15">
+      <c r="A83" t="s">
+        <v>1526</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>1021</v>
+      </c>
+      <c r="E83" s="2">
+        <v>0</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>1022</v>
+      </c>
+      <c r="G83" s="4" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H83" s="4" t="s">
+        <v>1024</v>
+      </c>
+      <c r="I83" s="2">
+        <v>0</v>
+      </c>
+      <c r="J83" s="4" t="s">
+        <v>1025</v>
+      </c>
+      <c r="K83" s="4" t="s">
+        <v>1026</v>
+      </c>
+      <c r="L83" s="4" t="s">
+        <v>1027</v>
+      </c>
+      <c r="M83" s="4" t="s">
+        <v>1028</v>
+      </c>
+      <c r="N83" s="4" t="s">
+        <v>1029</v>
+      </c>
+      <c r="O83" s="4" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15">
+      <c r="A84" t="s">
+        <v>1527</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E84" s="2">
+        <v>0</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>1034</v>
+      </c>
+      <c r="G84" s="4" t="s">
+        <v>1035</v>
+      </c>
+      <c r="H84" s="4" t="s">
+        <v>1036</v>
+      </c>
+      <c r="I84" s="2">
+        <v>0</v>
+      </c>
+      <c r="J84" s="4" t="s">
+        <v>1037</v>
+      </c>
+      <c r="K84" s="4" t="s">
+        <v>1038</v>
+      </c>
+      <c r="L84" s="4" t="s">
+        <v>1039</v>
+      </c>
+      <c r="M84" s="4" t="s">
+        <v>1040</v>
+      </c>
+      <c r="N84" s="4" t="s">
+        <v>1041</v>
+      </c>
+      <c r="O84" s="4" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15">
+      <c r="A85" t="s">
+        <v>1528</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E85" s="2">
+        <v>0</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>1046</v>
+      </c>
+      <c r="G85" s="4" t="s">
+        <v>1047</v>
+      </c>
+      <c r="H85" s="4" t="s">
+        <v>1048</v>
+      </c>
+      <c r="I85" s="2">
+        <v>0</v>
+      </c>
+      <c r="J85" s="4" t="s">
+        <v>1049</v>
+      </c>
+      <c r="K85" s="4" t="s">
+        <v>1050</v>
+      </c>
+      <c r="L85" s="4" t="s">
+        <v>1051</v>
+      </c>
+      <c r="M85" s="4" t="s">
+        <v>1052</v>
+      </c>
+      <c r="N85" s="4" t="s">
+        <v>1053</v>
+      </c>
+      <c r="O85" s="4" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15">
+      <c r="A86" t="s">
+        <v>1529</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>1057</v>
+      </c>
+      <c r="E86" s="2">
+        <v>0</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>1058</v>
+      </c>
+      <c r="G86" s="4" t="s">
+        <v>1059</v>
+      </c>
+      <c r="H86" s="4" t="s">
+        <v>1060</v>
+      </c>
+      <c r="I86" s="2">
+        <v>0</v>
+      </c>
+      <c r="J86" s="4" t="s">
+        <v>1061</v>
+      </c>
+      <c r="K86" s="4" t="s">
+        <v>1062</v>
+      </c>
+      <c r="L86" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="M86" s="4" t="s">
+        <v>1064</v>
+      </c>
+      <c r="N86" s="4" t="s">
+        <v>1065</v>
+      </c>
+      <c r="O86" s="4" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15">
+      <c r="A87" t="s">
+        <v>1530</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>1069</v>
+      </c>
+      <c r="E87" s="2">
+        <v>0</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>1070</v>
+      </c>
+      <c r="G87" s="4" t="s">
+        <v>1071</v>
+      </c>
+      <c r="H87" s="4" t="s">
+        <v>1072</v>
+      </c>
+      <c r="I87" s="2">
+        <v>0</v>
+      </c>
+      <c r="J87" s="4" t="s">
+        <v>1073</v>
+      </c>
+      <c r="K87" s="4" t="s">
+        <v>1074</v>
+      </c>
+      <c r="L87" s="4" t="s">
+        <v>1075</v>
+      </c>
+      <c r="M87" s="4" t="s">
+        <v>1076</v>
+      </c>
+      <c r="N87" s="4" t="s">
+        <v>1077</v>
+      </c>
+      <c r="O87" s="4" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15">
+      <c r="A88" t="s">
+        <v>1531</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>769</v>
+      </c>
+      <c r="E88" s="2">
+        <v>0</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>1081</v>
+      </c>
+      <c r="G88" s="4" t="s">
+        <v>1082</v>
+      </c>
+      <c r="H88" s="4" t="s">
+        <v>1083</v>
+      </c>
+      <c r="I88" s="2">
+        <v>0</v>
+      </c>
+      <c r="J88" s="4" t="s">
+        <v>1084</v>
+      </c>
+      <c r="K88" s="4" t="s">
+        <v>1085</v>
+      </c>
+      <c r="L88" s="4" t="s">
+        <v>1086</v>
+      </c>
+      <c r="M88" s="4" t="s">
+        <v>1087</v>
+      </c>
+      <c r="N88" s="4" t="s">
+        <v>1088</v>
+      </c>
+      <c r="O88" s="4" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15">
+      <c r="A89" t="s">
+        <v>1532</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>1092</v>
+      </c>
+      <c r="E89" s="2">
+        <v>0</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="G89" s="4" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H89" s="4" t="s">
+        <v>1095</v>
+      </c>
+      <c r="I89" s="2">
+        <v>0</v>
+      </c>
+      <c r="J89" s="4" t="s">
+        <v>1096</v>
+      </c>
+      <c r="K89" s="4" t="s">
+        <v>1097</v>
+      </c>
+      <c r="L89" s="4" t="s">
+        <v>1098</v>
+      </c>
+      <c r="M89" s="4" t="s">
+        <v>1099</v>
+      </c>
+      <c r="N89" s="4" t="s">
+        <v>1100</v>
+      </c>
+      <c r="O89" s="4" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15">
+      <c r="A90" t="s">
+        <v>1533</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E90" s="2">
+        <v>0</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>1105</v>
+      </c>
+      <c r="G90" s="4" t="s">
+        <v>1106</v>
+      </c>
+      <c r="H90" s="4" t="s">
+        <v>1107</v>
+      </c>
+      <c r="I90" s="2">
+        <v>0</v>
+      </c>
+      <c r="J90" s="4" t="s">
+        <v>1108</v>
+      </c>
+      <c r="K90" s="4" t="s">
+        <v>1109</v>
+      </c>
+      <c r="L90" s="4" t="s">
+        <v>1110</v>
+      </c>
+      <c r="M90" s="4" t="s">
+        <v>1111</v>
+      </c>
+      <c r="N90" s="4" t="s">
+        <v>1112</v>
+      </c>
+      <c r="O90" s="4" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15">
+      <c r="A91" t="s">
+        <v>1534</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>1115</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E91" s="2">
+        <v>0</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>1117</v>
+      </c>
+      <c r="G91" s="4" t="s">
+        <v>1118</v>
+      </c>
+      <c r="H91" s="4" t="s">
+        <v>1119</v>
+      </c>
+      <c r="I91" s="2">
+        <v>0</v>
+      </c>
+      <c r="J91" s="4" t="s">
+        <v>1120</v>
+      </c>
+      <c r="K91" s="4" t="s">
+        <v>1121</v>
+      </c>
+      <c r="L91" s="4" t="s">
+        <v>1122</v>
+      </c>
+      <c r="M91" s="4" t="s">
+        <v>1123</v>
+      </c>
+      <c r="N91" s="4" t="s">
+        <v>1124</v>
+      </c>
+      <c r="O91" s="4" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15">
+      <c r="A92" t="s">
+        <v>1535</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E92" s="2">
+        <v>0</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>1129</v>
+      </c>
+      <c r="G92" s="4" t="s">
+        <v>1130</v>
+      </c>
+      <c r="H92" s="4" t="s">
+        <v>1131</v>
+      </c>
+      <c r="I92" s="2">
+        <v>0</v>
+      </c>
+      <c r="J92" s="4" t="s">
+        <v>1132</v>
+      </c>
+      <c r="K92" s="4" t="s">
+        <v>1133</v>
+      </c>
+      <c r="L92" s="4" t="s">
+        <v>1134</v>
+      </c>
+      <c r="M92" s="4" t="s">
+        <v>1135</v>
+      </c>
+      <c r="N92" s="4" t="s">
+        <v>1136</v>
+      </c>
+      <c r="O92" s="4" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15">
+      <c r="A93" t="s">
+        <v>1536</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>1140</v>
+      </c>
+      <c r="E93" s="2">
+        <v>0</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>1141</v>
+      </c>
+      <c r="G93" s="4" t="s">
+        <v>1142</v>
+      </c>
+      <c r="H93" s="4" t="s">
+        <v>1143</v>
+      </c>
+      <c r="I93" s="2">
+        <v>0</v>
+      </c>
+      <c r="J93" s="4" t="s">
+        <v>1144</v>
+      </c>
+      <c r="K93" s="4" t="s">
+        <v>1145</v>
+      </c>
+      <c r="L93" s="4" t="s">
+        <v>1146</v>
+      </c>
+      <c r="M93" s="4" t="s">
+        <v>1147</v>
+      </c>
+      <c r="N93" s="4" t="s">
+        <v>1148</v>
+      </c>
+      <c r="O93" s="4" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15">
+      <c r="A94" t="s">
+        <v>1537</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>1151</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>1152</v>
+      </c>
+      <c r="E94" s="2">
+        <v>0</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>1153</v>
+      </c>
+      <c r="G94" s="4" t="s">
+        <v>1154</v>
+      </c>
+      <c r="H94" s="4" t="s">
+        <v>1155</v>
+      </c>
+      <c r="I94" s="2">
+        <v>0</v>
+      </c>
+      <c r="J94" s="4" t="s">
+        <v>1156</v>
+      </c>
+      <c r="K94" s="4" t="s">
+        <v>1157</v>
+      </c>
+      <c r="L94" s="4" t="s">
+        <v>1158</v>
+      </c>
+      <c r="M94" s="4" t="s">
+        <v>1159</v>
+      </c>
+      <c r="N94" s="4" t="s">
+        <v>1160</v>
+      </c>
+      <c r="O94" s="4" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15">
+      <c r="A95" t="s">
+        <v>1538</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>1163</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>1164</v>
+      </c>
+      <c r="E95" s="2">
+        <v>0</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>1165</v>
+      </c>
+      <c r="G95" s="4" t="s">
+        <v>1166</v>
+      </c>
+      <c r="H95" s="4" t="s">
+        <v>1167</v>
+      </c>
+      <c r="I95" s="2">
+        <v>0</v>
+      </c>
+      <c r="J95" s="4" t="s">
+        <v>1168</v>
+      </c>
+      <c r="K95" s="4" t="s">
+        <v>1169</v>
+      </c>
+      <c r="L95" s="4" t="s">
+        <v>1170</v>
+      </c>
+      <c r="M95" s="4" t="s">
+        <v>1171</v>
+      </c>
+      <c r="N95" s="4" t="s">
+        <v>1172</v>
+      </c>
+      <c r="O95" s="4" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15">
+      <c r="A96" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>1175</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>1176</v>
+      </c>
+      <c r="E96" s="2">
+        <v>0</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>1177</v>
+      </c>
+      <c r="G96" s="4" t="s">
+        <v>1178</v>
+      </c>
+      <c r="H96" s="4" t="s">
+        <v>1179</v>
+      </c>
+      <c r="I96" s="2">
+        <v>0</v>
+      </c>
+      <c r="J96" s="4" t="s">
+        <v>1180</v>
+      </c>
+      <c r="K96" s="4" t="s">
+        <v>1181</v>
+      </c>
+      <c r="L96" s="4" t="s">
+        <v>1182</v>
+      </c>
+      <c r="M96" s="4" t="s">
+        <v>1183</v>
+      </c>
+      <c r="N96" s="4" t="s">
+        <v>1184</v>
+      </c>
+      <c r="O96" s="4" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15">
+      <c r="A97" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>1187</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>1188</v>
+      </c>
+      <c r="E97" s="2">
+        <v>0</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>1189</v>
+      </c>
+      <c r="G97" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="H97" s="4" t="s">
+        <v>1191</v>
+      </c>
+      <c r="I97" s="2">
+        <v>0</v>
+      </c>
+      <c r="J97" s="4" t="s">
+        <v>1192</v>
+      </c>
+      <c r="K97" s="4" t="s">
+        <v>1193</v>
+      </c>
+      <c r="L97" s="4" t="s">
+        <v>1194</v>
+      </c>
+      <c r="M97" s="4" t="s">
+        <v>1195</v>
+      </c>
+      <c r="N97" s="4" t="s">
+        <v>1196</v>
+      </c>
+      <c r="O97" s="4" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15">
+      <c r="A98" t="s">
+        <v>1541</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>1199</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E98" s="2">
+        <v>0</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>1201</v>
+      </c>
+      <c r="G98" s="4" t="s">
+        <v>1202</v>
+      </c>
+      <c r="H98" s="4" t="s">
+        <v>1203</v>
+      </c>
+      <c r="I98" s="2">
+        <v>0</v>
+      </c>
+      <c r="J98" s="4" t="s">
+        <v>1204</v>
+      </c>
+      <c r="K98" s="4" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L98" s="4" t="s">
+        <v>1206</v>
+      </c>
+      <c r="M98" s="4" t="s">
+        <v>1207</v>
+      </c>
+      <c r="N98" s="4" t="s">
+        <v>1208</v>
+      </c>
+      <c r="O98" s="4" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15">
+      <c r="A99" t="s">
+        <v>1542</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>1212</v>
+      </c>
+      <c r="E99" s="2">
+        <v>0</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>1213</v>
+      </c>
+      <c r="G99" s="4" t="s">
+        <v>1214</v>
+      </c>
+      <c r="H99" s="4" t="s">
+        <v>1215</v>
+      </c>
+      <c r="I99" s="2">
+        <v>0</v>
+      </c>
+      <c r="J99" s="4" t="s">
+        <v>1216</v>
+      </c>
+      <c r="K99" s="4" t="s">
+        <v>1217</v>
+      </c>
+      <c r="L99" s="4" t="s">
+        <v>1218</v>
+      </c>
+      <c r="M99" s="4" t="s">
+        <v>1219</v>
+      </c>
+      <c r="N99" s="4" t="s">
+        <v>1220</v>
+      </c>
+      <c r="O99" s="4" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15">
+      <c r="A100" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>1224</v>
+      </c>
+      <c r="E100" s="2">
+        <v>0</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>1225</v>
+      </c>
+      <c r="G100" s="4" t="s">
+        <v>1226</v>
+      </c>
+      <c r="H100" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="I100" s="2">
+        <v>0</v>
+      </c>
+      <c r="J100" s="4" t="s">
+        <v>1228</v>
+      </c>
+      <c r="K100" s="4" t="s">
+        <v>1229</v>
+      </c>
+      <c r="L100" s="4" t="s">
+        <v>1230</v>
+      </c>
+      <c r="M100" s="4" t="s">
+        <v>1231</v>
+      </c>
+      <c r="N100" s="4" t="s">
+        <v>1232</v>
+      </c>
+      <c r="O100" s="4" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15">
+      <c r="A101" t="s">
+        <v>1544</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>1235</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>1236</v>
+      </c>
+      <c r="E101" s="2">
+        <v>0</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>1237</v>
+      </c>
+      <c r="G101" s="4" t="s">
+        <v>1238</v>
+      </c>
+      <c r="H101" s="4" t="s">
+        <v>1239</v>
+      </c>
+      <c r="I101" s="2">
+        <v>0</v>
+      </c>
+      <c r="J101" s="4" t="s">
+        <v>1240</v>
+      </c>
+      <c r="K101" s="4" t="s">
+        <v>1241</v>
+      </c>
+      <c r="L101" s="4" t="s">
+        <v>1242</v>
+      </c>
+      <c r="M101" s="4" t="s">
+        <v>1243</v>
+      </c>
+      <c r="N101" s="4" t="s">
+        <v>1244</v>
+      </c>
+      <c r="O101" s="4" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15">
+      <c r="A102" t="s">
+        <v>1545</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>1248</v>
+      </c>
+      <c r="E102" s="2">
+        <v>0</v>
+      </c>
+      <c r="F102" s="4" t="s">
+        <v>1249</v>
+      </c>
+      <c r="G102" s="4" t="s">
+        <v>1250</v>
+      </c>
+      <c r="H102" s="4" t="s">
+        <v>1251</v>
+      </c>
+      <c r="I102" s="2">
+        <v>0</v>
+      </c>
+      <c r="J102" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="K102" s="4" t="s">
+        <v>1253</v>
+      </c>
+      <c r="L102" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="M102" s="4" t="s">
+        <v>1255</v>
+      </c>
+      <c r="N102" s="4" t="s">
+        <v>1256</v>
+      </c>
+      <c r="O102" s="4" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15">
+      <c r="A103" t="s">
+        <v>1546</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>1259</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>1260</v>
+      </c>
+      <c r="E103" s="2">
+        <v>0</v>
+      </c>
+      <c r="F103" s="4" t="s">
+        <v>1261</v>
+      </c>
+      <c r="G103" s="4" t="s">
+        <v>1262</v>
+      </c>
+      <c r="H103" s="4" t="s">
+        <v>1263</v>
+      </c>
+      <c r="I103" s="2">
+        <v>0</v>
+      </c>
+      <c r="J103" s="4" t="s">
+        <v>1264</v>
+      </c>
+      <c r="K103" s="4" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L103" s="4" t="s">
+        <v>1266</v>
+      </c>
+      <c r="M103" s="4" t="s">
+        <v>1267</v>
+      </c>
+      <c r="N103" s="4" t="s">
+        <v>1268</v>
+      </c>
+      <c r="O103" s="4" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15">
+      <c r="A104" t="s">
+        <v>1547</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>1271</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>1272</v>
+      </c>
+      <c r="E104" s="2">
+        <v>0</v>
+      </c>
+      <c r="F104" s="4" t="s">
+        <v>1273</v>
+      </c>
+      <c r="G104" s="4" t="s">
+        <v>1274</v>
+      </c>
+      <c r="H104" s="4" t="s">
+        <v>1275</v>
+      </c>
+      <c r="I104" s="2">
+        <v>0</v>
+      </c>
+      <c r="J104" s="4" t="s">
+        <v>1276</v>
+      </c>
+      <c r="K104" s="4" t="s">
+        <v>1277</v>
+      </c>
+      <c r="L104" s="4" t="s">
+        <v>1278</v>
+      </c>
+      <c r="M104" s="4" t="s">
+        <v>1279</v>
+      </c>
+      <c r="N104" s="4" t="s">
+        <v>1280</v>
+      </c>
+      <c r="O104" s="4" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15">
+      <c r="A105" t="s">
+        <v>1548</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>1283</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>1284</v>
+      </c>
+      <c r="E105" s="2">
+        <v>0</v>
+      </c>
+      <c r="F105" s="4" t="s">
+        <v>1285</v>
+      </c>
+      <c r="G105" s="4" t="s">
+        <v>1286</v>
+      </c>
+      <c r="H105" s="4" t="s">
+        <v>1287</v>
+      </c>
+      <c r="I105" s="2">
+        <v>0</v>
+      </c>
+      <c r="J105" s="4" t="s">
+        <v>1288</v>
+      </c>
+      <c r="K105" s="4" t="s">
+        <v>1289</v>
+      </c>
+      <c r="L105" s="4" t="s">
+        <v>1290</v>
+      </c>
+      <c r="M105" s="4" t="s">
+        <v>1291</v>
+      </c>
+      <c r="N105" s="4" t="s">
+        <v>1292</v>
+      </c>
+      <c r="O105" s="4" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15">
+      <c r="A106" t="s">
+        <v>1549</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>1295</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>1296</v>
+      </c>
+      <c r="E106" s="2">
+        <v>0</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>1297</v>
+      </c>
+      <c r="G106" s="4" t="s">
+        <v>1298</v>
+      </c>
+      <c r="H106" s="4" t="s">
+        <v>1299</v>
+      </c>
+      <c r="I106" s="2">
+        <v>0</v>
+      </c>
+      <c r="J106" s="4" t="s">
+        <v>1300</v>
+      </c>
+      <c r="K106" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="L106" s="4" t="s">
+        <v>1302</v>
+      </c>
+      <c r="M106" s="4" t="s">
+        <v>1303</v>
+      </c>
+      <c r="N106" s="4" t="s">
+        <v>1304</v>
+      </c>
+      <c r="O106" s="4" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15">
+      <c r="A107" t="s">
+        <v>1550</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>1307</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="E107" s="2">
+        <v>0</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>1309</v>
+      </c>
+      <c r="G107" s="4" t="s">
+        <v>1310</v>
+      </c>
+      <c r="H107" s="4" t="s">
+        <v>1311</v>
+      </c>
+      <c r="I107" s="2">
+        <v>0</v>
+      </c>
+      <c r="J107" s="4" t="s">
+        <v>1312</v>
+      </c>
+      <c r="K107" s="4" t="s">
+        <v>1313</v>
+      </c>
+      <c r="L107" s="4" t="s">
+        <v>1314</v>
+      </c>
+      <c r="M107" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="N107" s="4" t="s">
+        <v>1316</v>
+      </c>
+      <c r="O107" s="4" t="s">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15">
+      <c r="A108" t="s">
+        <v>1551</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>1319</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>1320</v>
+      </c>
+      <c r="E108" s="2">
+        <v>0</v>
+      </c>
+      <c r="F108" s="4" t="s">
+        <v>1321</v>
+      </c>
+      <c r="G108" s="4" t="s">
+        <v>1322</v>
+      </c>
+      <c r="H108" s="4" t="s">
+        <v>1323</v>
+      </c>
+      <c r="I108" s="2">
+        <v>0</v>
+      </c>
+      <c r="J108" s="4" t="s">
+        <v>1324</v>
+      </c>
+      <c r="K108" s="4" t="s">
+        <v>1325</v>
+      </c>
+      <c r="L108" s="4" t="s">
+        <v>1326</v>
+      </c>
+      <c r="M108" s="4" t="s">
+        <v>1327</v>
+      </c>
+      <c r="N108" s="4" t="s">
+        <v>1328</v>
+      </c>
+      <c r="O108" s="4" t="s">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15">
+      <c r="A109" t="s">
+        <v>1552</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>1330</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>1331</v>
+      </c>
+      <c r="D109" s="4" t="s">
+        <v>1332</v>
+      </c>
+      <c r="E109" s="2">
+        <v>0</v>
+      </c>
+      <c r="F109" s="4" t="s">
+        <v>1333</v>
+      </c>
+      <c r="G109" s="4" t="s">
+        <v>1334</v>
+      </c>
+      <c r="H109" s="4" t="s">
+        <v>1335</v>
+      </c>
+      <c r="I109" s="2">
+        <v>0</v>
+      </c>
+      <c r="J109" s="4" t="s">
+        <v>1336</v>
+      </c>
+      <c r="K109" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="L109" s="4" t="s">
+        <v>1338</v>
+      </c>
+      <c r="M109" s="4" t="s">
+        <v>1339</v>
+      </c>
+      <c r="N109" s="4" t="s">
+        <v>1340</v>
+      </c>
+      <c r="O109" s="4" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15">
+      <c r="A110" t="s">
+        <v>1553</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>1342</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>1343</v>
+      </c>
+      <c r="D110" s="4" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E110" s="2">
+        <v>0</v>
+      </c>
+      <c r="F110" s="4" t="s">
+        <v>1345</v>
+      </c>
+      <c r="G110" s="4" t="s">
+        <v>1346</v>
+      </c>
+      <c r="H110" s="4" t="s">
+        <v>1347</v>
+      </c>
+      <c r="I110" s="2">
+        <v>0</v>
+      </c>
+      <c r="J110" s="4" t="s">
+        <v>1348</v>
+      </c>
+      <c r="K110" s="4" t="s">
+        <v>1349</v>
+      </c>
+      <c r="L110" s="4" t="s">
+        <v>1350</v>
+      </c>
+      <c r="M110" s="4" t="s">
+        <v>1351</v>
+      </c>
+      <c r="N110" s="4" t="s">
+        <v>1352</v>
+      </c>
+      <c r="O110" s="4" t="s">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15">
+      <c r="A111" t="s">
+        <v>1554</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>1355</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>1356</v>
+      </c>
+      <c r="E111" s="2">
+        <v>0</v>
+      </c>
+      <c r="F111" s="4" t="s">
+        <v>1357</v>
+      </c>
+      <c r="G111" s="4" t="s">
+        <v>1358</v>
+      </c>
+      <c r="H111" s="4" t="s">
+        <v>1359</v>
+      </c>
+      <c r="I111" s="2">
+        <v>0</v>
+      </c>
+      <c r="J111" s="4" t="s">
+        <v>1360</v>
+      </c>
+      <c r="K111" s="4" t="s">
+        <v>1361</v>
+      </c>
+      <c r="L111" s="4" t="s">
+        <v>1362</v>
+      </c>
+      <c r="M111" s="4" t="s">
+        <v>1363</v>
+      </c>
+      <c r="N111" s="4" t="s">
+        <v>1364</v>
+      </c>
+      <c r="O111" s="4" t="s">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15">
+      <c r="A112" t="s">
+        <v>1555</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>1367</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>1368</v>
+      </c>
+      <c r="E112" s="2">
+        <v>0</v>
+      </c>
+      <c r="F112" s="4" t="s">
+        <v>1369</v>
+      </c>
+      <c r="G112" s="4" t="s">
+        <v>1370</v>
+      </c>
+      <c r="H112" s="4" t="s">
+        <v>1371</v>
+      </c>
+      <c r="I112" s="2">
+        <v>0</v>
+      </c>
+      <c r="J112" s="4" t="s">
+        <v>1372</v>
+      </c>
+      <c r="K112" s="4" t="s">
+        <v>1373</v>
+      </c>
+      <c r="L112" s="4" t="s">
+        <v>1374</v>
+      </c>
+      <c r="M112" s="4" t="s">
+        <v>1375</v>
+      </c>
+      <c r="N112" s="4" t="s">
+        <v>1376</v>
+      </c>
+      <c r="O112" s="4" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15">
+      <c r="A113" t="s">
+        <v>1556</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>1378</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>1379</v>
+      </c>
+      <c r="D113" s="4" t="s">
+        <v>1380</v>
+      </c>
+      <c r="E113" s="2">
+        <v>0</v>
+      </c>
+      <c r="F113" s="4" t="s">
+        <v>1381</v>
+      </c>
+      <c r="G113" s="4" t="s">
+        <v>1382</v>
+      </c>
+      <c r="H113" s="4" t="s">
+        <v>1383</v>
+      </c>
+      <c r="I113" s="2">
+        <v>0</v>
+      </c>
+      <c r="J113" s="4" t="s">
+        <v>1384</v>
+      </c>
+      <c r="K113" s="4" t="s">
+        <v>1385</v>
+      </c>
+      <c r="L113" s="4" t="s">
+        <v>1386</v>
+      </c>
+      <c r="M113" s="4" t="s">
+        <v>1387</v>
+      </c>
+      <c r="N113" s="4" t="s">
+        <v>1388</v>
+      </c>
+      <c r="O113" s="4" t="s">
+        <v>1389</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15">
+      <c r="A114" t="s">
+        <v>1557</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>1390</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>1391</v>
+      </c>
+      <c r="D114" s="4" t="s">
+        <v>1347</v>
+      </c>
+      <c r="E114" s="2">
+        <v>0</v>
+      </c>
+      <c r="F114" s="4" t="s">
+        <v>1392</v>
+      </c>
+      <c r="G114" s="4" t="s">
+        <v>1393</v>
+      </c>
+      <c r="H114" s="4" t="s">
+        <v>1394</v>
+      </c>
+      <c r="I114" s="2">
+        <v>0</v>
+      </c>
+      <c r="J114" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="K114" s="4" t="s">
+        <v>1396</v>
+      </c>
+      <c r="L114" s="4" t="s">
+        <v>1397</v>
+      </c>
+      <c r="M114" s="4" t="s">
+        <v>1398</v>
+      </c>
+      <c r="N114" s="4" t="s">
+        <v>1399</v>
+      </c>
+      <c r="O114" s="4" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15">
+      <c r="A115" t="s">
+        <v>1558</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>1401</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>1402</v>
+      </c>
+      <c r="D115" s="4" t="s">
+        <v>1403</v>
+      </c>
+      <c r="E115" s="2">
+        <v>0</v>
+      </c>
+      <c r="F115" s="4" t="s">
+        <v>1404</v>
+      </c>
+      <c r="G115" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="H115" s="4" t="s">
+        <v>1406</v>
+      </c>
+      <c r="I115" s="2">
+        <v>0</v>
+      </c>
+      <c r="J115" s="4" t="s">
+        <v>1407</v>
+      </c>
+      <c r="K115" s="4" t="s">
+        <v>1408</v>
+      </c>
+      <c r="L115" s="4" t="s">
+        <v>1409</v>
+      </c>
+      <c r="M115" s="4" t="s">
+        <v>1410</v>
+      </c>
+      <c r="N115" s="4" t="s">
+        <v>1411</v>
+      </c>
+      <c r="O115" s="4" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15">
+      <c r="A116" t="s">
+        <v>1559</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>1413</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D116" s="4" t="s">
+        <v>1415</v>
+      </c>
+      <c r="E116" s="2">
+        <v>0</v>
+      </c>
+      <c r="F116" s="4" t="s">
+        <v>1416</v>
+      </c>
+      <c r="G116" s="4" t="s">
+        <v>1417</v>
+      </c>
+      <c r="H116" s="4" t="s">
+        <v>1418</v>
+      </c>
+      <c r="I116" s="2">
+        <v>0</v>
+      </c>
+      <c r="J116" s="4" t="s">
+        <v>1419</v>
+      </c>
+      <c r="K116" s="4" t="s">
+        <v>1420</v>
+      </c>
+      <c r="L116" s="4" t="s">
+        <v>1421</v>
+      </c>
+      <c r="M116" s="4" t="s">
+        <v>1422</v>
+      </c>
+      <c r="N116" s="4" t="s">
+        <v>1423</v>
+      </c>
+      <c r="O116" s="4" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15">
+      <c r="A117" t="s">
+        <v>1560</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>1425</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>1426</v>
+      </c>
+      <c r="D117" s="4" t="s">
+        <v>1427</v>
+      </c>
+      <c r="E117" s="2">
+        <v>0</v>
+      </c>
+      <c r="F117" s="4" t="s">
+        <v>1428</v>
+      </c>
+      <c r="G117" s="4" t="s">
+        <v>1429</v>
+      </c>
+      <c r="H117" s="4" t="s">
+        <v>1430</v>
+      </c>
+      <c r="I117" s="2">
+        <v>0</v>
+      </c>
+      <c r="J117" s="4" t="s">
+        <v>1431</v>
+      </c>
+      <c r="K117" s="4" t="s">
+        <v>1432</v>
+      </c>
+      <c r="L117" s="4" t="s">
+        <v>1433</v>
+      </c>
+      <c r="M117" s="4" t="s">
+        <v>1434</v>
+      </c>
+      <c r="N117" s="4" t="s">
+        <v>1435</v>
+      </c>
+      <c r="O117" s="4" t="s">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15">
+      <c r="A118" t="s">
+        <v>1561</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>1437</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>1438</v>
+      </c>
+      <c r="D118" s="4" t="s">
+        <v>1439</v>
+      </c>
+      <c r="E118" s="2">
+        <v>0</v>
+      </c>
+      <c r="F118" s="4" t="s">
+        <v>1440</v>
+      </c>
+      <c r="G118" s="4" t="s">
+        <v>1441</v>
+      </c>
+      <c r="H118" s="4" t="s">
+        <v>1442</v>
+      </c>
+      <c r="I118" s="2">
+        <v>0</v>
+      </c>
+      <c r="J118" s="4" t="s">
+        <v>1443</v>
+      </c>
+      <c r="K118" s="4" t="s">
+        <v>1444</v>
+      </c>
+      <c r="L118" s="4" t="s">
+        <v>1445</v>
+      </c>
+      <c r="M118" s="4" t="s">
+        <v>1446</v>
+      </c>
+      <c r="N118" s="4" t="s">
+        <v>1447</v>
+      </c>
+      <c r="O118" s="4" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15">
+      <c r="A119" t="s">
+        <v>1562</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>1449</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>1450</v>
+      </c>
+      <c r="D119" s="4" t="s">
+        <v>1451</v>
+      </c>
+      <c r="E119" s="2">
+        <v>0</v>
+      </c>
+      <c r="F119" s="4" t="s">
+        <v>1452</v>
+      </c>
+      <c r="G119" s="4" t="s">
+        <v>1453</v>
+      </c>
+      <c r="H119" s="4" t="s">
+        <v>1454</v>
+      </c>
+      <c r="I119" s="2">
+        <v>0</v>
+      </c>
+      <c r="J119" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="K119" s="4" t="s">
+        <v>1456</v>
+      </c>
+      <c r="L119" s="4" t="s">
+        <v>1457</v>
+      </c>
+      <c r="M119" s="4" t="s">
+        <v>1458</v>
+      </c>
+      <c r="N119" s="4" t="s">
+        <v>1459</v>
+      </c>
+      <c r="O119" s="4" t="s">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15">
+      <c r="A120" t="s">
+        <v>1563</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>1461</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>1462</v>
+      </c>
+      <c r="D120" s="4" t="s">
+        <v>1463</v>
+      </c>
+      <c r="E120" s="2">
+        <v>0</v>
+      </c>
+      <c r="F120" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G120" s="4" t="s">
+        <v>1465</v>
+      </c>
+      <c r="H120" s="4" t="s">
+        <v>1466</v>
+      </c>
+      <c r="I120" s="2">
+        <v>0</v>
+      </c>
+      <c r="J120" s="4" t="s">
+        <v>1467</v>
+      </c>
+      <c r="K120" s="4" t="s">
+        <v>1468</v>
+      </c>
+      <c r="L120" s="4" t="s">
+        <v>1469</v>
+      </c>
+      <c r="M120" s="4" t="s">
+        <v>1470</v>
+      </c>
+      <c r="N120" s="4" t="s">
+        <v>1471</v>
+      </c>
+      <c r="O120" s="4" t="s">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15">
+      <c r="A121" t="s">
+        <v>1564</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>1473</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>1474</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>1475</v>
+      </c>
+      <c r="E121" s="2">
+        <v>0</v>
+      </c>
+      <c r="F121" s="4" t="s">
+        <v>1476</v>
+      </c>
+      <c r="G121" s="4" t="s">
+        <v>1477</v>
+      </c>
+      <c r="H121" s="4" t="s">
+        <v>1478</v>
+      </c>
+      <c r="I121" s="2">
+        <v>0</v>
+      </c>
+      <c r="J121" s="4" t="s">
+        <v>1479</v>
+      </c>
+      <c r="K121" s="4" t="s">
+        <v>1480</v>
+      </c>
+      <c r="L121" s="4" t="s">
+        <v>1481</v>
+      </c>
+      <c r="M121" s="4" t="s">
+        <v>1482</v>
+      </c>
+      <c r="N121" s="4" t="s">
+        <v>1483</v>
+      </c>
+      <c r="O121" s="4" t="s">
+        <v>1484</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>